--- a/reports/devops-juniors-israel-2026-W37.xlsx
+++ b/reports/devops-juniors-israel-2026-W37.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="267">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07T12:20:42</t>
+    <t xml:space="preserve">2026-09-08T11:09:39</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -91,12 +91,12 @@
     <t xml:space="preserve">By bucket</t>
   </si>
   <si>
+    <t xml:space="preserve">SysAdmin / NOC</t>
+  </si>
+  <si>
     <t xml:space="preserve">Help Desk / IT Support</t>
   </si>
   <si>
-    <t xml:space="preserve">SysAdmin / NOC</t>
-  </si>
-  <si>
     <t xml:space="preserve">Trainee / Bootcamp Grad</t>
   </si>
   <si>
@@ -145,6 +145,24 @@
     <t xml:space="preserve">First Seen</t>
   </si>
   <si>
+    <t xml:space="preserve">Student DevOps Engineer- CxP Commercial Foundation Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Terraform/IaC, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-devops-engineer-cxp-commercial-foundation-services-at-sap-4436819328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-20</t>
+  </si>
+  <si>
     <t xml:space="preserve">NOC Team Leader</t>
   </si>
   <si>
@@ -160,7 +178,70 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-team-leader-at-rapyd-4428470164</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-20</t>
+    <t xml:space="preserve">Linux System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calanit by one</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-calanit-by-one-4464446970</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator / DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SuperCom (NASDAQ: SPCB)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, Cloud (any), CI/CD, Git, Networking, Monitoring, Databases, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-devops-at-supercom-nasdaq-spcb-4464376479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-supercom-nasdaq-spcb-4462293466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">comblack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), CI/CD, Git, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-comblack-4464346266</t>
   </si>
   <si>
     <t xml:space="preserve">Devops Student</t>
@@ -244,7 +325,22 @@
     <t xml:space="preserve">2026-08-31</t>
   </si>
   <si>
-    <t xml:space="preserve">System Administrator</t>
+    <t xml:space="preserve">Computer System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Camtek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Migdal HaEmek, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/computer-system-engineer-at-camtek-4432772061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-02</t>
   </si>
   <si>
     <t xml:space="preserve">CONTROP Precision Technologies Ltd.</t>
@@ -262,24 +358,6 @@
     <t xml:space="preserve">2026-09-02</t>
   </si>
   <si>
-    <t xml:space="preserve">Technical Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upwind Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Networking, Monitoring, Databases, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-upwind-security-4460871956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-30</t>
-  </si>
-  <si>
     <t xml:space="preserve">Technical Support Engineer</t>
   </si>
   <si>
@@ -319,9 +397,6 @@
     <t xml:space="preserve">OnCloud</t>
   </si>
   <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Active Directory</t>
   </si>
   <si>
@@ -331,6 +406,21 @@
     <t xml:space="preserve">2026-08-26</t>
   </si>
   <si>
+    <t xml:space="preserve">TytoCare</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-tytocare-4461579939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-01</t>
+  </si>
+  <si>
     <t xml:space="preserve">System Administrator - 243425</t>
   </si>
   <si>
@@ -346,114 +436,153 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-243425-at-experis-israel-4461821675</t>
   </si>
   <si>
-    <t xml:space="preserve">IT Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UVeye</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Active Directory, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-uveye-4464029135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Engineering INTERN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft</t>
+    <t xml:space="preserve">IT Operations &amp; Security Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PointFive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Cloud (any), Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-security-specialist-at-pointfive-4426311043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raft Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4433796227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yael Korentec Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Virtualization, Active Directory, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-yael-korentec-technologies-4462122131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gini-Apps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Networking, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-gini-apps-4440026223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fetcherr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, CI/CD, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-fetcherr-4449296509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Field Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mornex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-field-support-engineer-at-mornex-4457946363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs JD Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator (24/7 Shift-Based)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">evoke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-24-7-shift-based-at-evoke-4462157700</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Systems Engineer 2, Technical Operations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oracle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineer-2-technical-operations-at-oracle-4441078871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Center IT Technician - Masmiya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nebius</t>
   </si>
   <si>
     <t xml:space="preserve">Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">Python, Cloud (any), CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineering-intern-at-microsoft-4451071541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yael Korentec Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Virtualization, Active Directory, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-yael-korentec-technologies-4462122131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gini-Apps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Networking, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-gini-apps-4440026223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fetcherr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-fetcherr-4449296509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Field Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mornex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-field-support-engineer-at-mornex-4457946363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator (24/7 Shift-Based)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">evoke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-24-7-shift-based-at-evoke-4462157700</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Center IT Technician - Masmiya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nebius</t>
-  </si>
-  <si>
     <t xml:space="preserve">Linux, Cloud (any), Networking, Monitoring, Troubleshooting</t>
   </si>
   <si>
@@ -478,6 +607,15 @@
     <t xml:space="preserve">2026-08-06</t>
   </si>
   <si>
+    <t xml:space="preserve">Tata Consultancy Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-tata-consultancy-services-4459788315</t>
+  </si>
+  <si>
     <t xml:space="preserve">NOC Israel</t>
   </si>
   <si>
@@ -499,27 +637,12 @@
     <t xml:space="preserve">Estonia</t>
   </si>
   <si>
-    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
   </si>
   <si>
     <t xml:space="preserve">2026-08-24</t>
   </si>
   <si>
-    <t xml:space="preserve">IT Support Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">comblack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-technician-at-comblack-4464328677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-07</t>
-  </si>
-  <si>
     <t xml:space="preserve">Junior System Administrator</t>
   </si>
   <si>
@@ -532,37 +655,19 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-administrator-at-com-c-tech-ltd-4457234117</t>
   </si>
   <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs JD Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days Open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Platform Engineer - Student (Java)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SAP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raanana, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-engineer-student-java-at-sap-4457493270</t>
+    <t xml:space="preserve">NOC Engineer- Student Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Global-e</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-student-position-at-global-e-4455188600</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-21</t>
   </si>
   <si>
     <t xml:space="preserve">Employer Branding Student (Temporary )</t>
@@ -574,9 +679,6 @@
     <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4912601101?gh_jid=4912601101</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-02</t>
-  </si>
-  <si>
     <t xml:space="preserve">Working Student, Legal (German-speaking)</t>
   </si>
   <si>
@@ -604,40 +706,58 @@
     <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
   </si>
   <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
+  </si>
+  <si>
     <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
   </si>
   <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
+    <t xml:space="preserve">Monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
   </si>
   <si>
     <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
   </si>
   <si>
-    <t xml:space="preserve">Monitoring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
-  </si>
-  <si>
     <t xml:space="preserve">Automation</t>
   </si>
   <si>
     <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
   </si>
   <si>
+    <t xml:space="preserve">Bash/Shell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
+  </si>
+  <si>
     <t xml:space="preserve">Python</t>
   </si>
   <si>
     <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
   </si>
   <si>
-    <t xml:space="preserve">Bash/Shell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
   </si>
   <si>
     <t xml:space="preserve">Active Directory</t>
@@ -646,40 +766,19 @@
     <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
   </si>
   <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free Docker Get Started tutorial + build 3 home-lab containers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kubernetes.io tutorials → minikube on laptop → KCNA cert</t>
+    <t xml:space="preserve">Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
   </si>
   <si>
     <t xml:space="preserve">Windows Server</t>
   </si>
   <si>
-    <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
+    <t xml:space="preserve">Git</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pro Git book (free online) + create a learning repo</t>
   </si>
   <si>
     <t xml:space="preserve">Count</t>
@@ -688,10 +787,10 @@
     <t xml:space="preserve">Pivot path advice</t>
   </si>
   <si>
+    <t xml:space="preserve">Already in IT — strengthen Linux + automation → apply to DevOps in 12-18mo.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tier 1/2 → SysAdmin → Junior DevOps. ~24 month path.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Already in IT — strengthen Linux + automation → apply to DevOps in 12-18mo.</t>
   </si>
   <si>
     <t xml:space="preserve">Cyclical — surge after bootcamp graduations (Aug/Feb).</t>
@@ -840,7 +939,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>28</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7">
@@ -848,7 +947,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -856,7 +955,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9">
@@ -864,7 +963,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>524</v>
+        <v>518</v>
       </c>
     </row>
     <row r="10">
@@ -946,7 +1045,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="22">
@@ -954,7 +1053,7 @@
         <v>26</v>
       </c>
       <c r="B22" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23">
@@ -962,7 +1061,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24">
@@ -996,7 +1095,7 @@
         <v>31</v>
       </c>
       <c r="B28" s="3">
-        <v>23</v>
+        <v>32</v>
       </c>
     </row>
     <row r="29">
@@ -1015,7 +1114,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="46" customWidth="1"/>
+    <col min="2" max="2" width="60" customWidth="1"/>
     <col min="3" max="3" width="37" customWidth="1"/>
     <col min="4" max="4" width="42" customWidth="1"/>
     <col min="5" max="5" width="31" customWidth="1"/>
@@ -1072,7 +1171,7 @@
         <v>45</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
@@ -1104,22 +1203,22 @@
         <v>51</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F3" s="3">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>52</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I3" s="3" t="s">
         <v>53</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4">
@@ -1127,19 +1226,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>45</v>
-      </c>
       <c r="E4" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F4" s="3">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>57</v>
@@ -1165,25 +1264,25 @@
         <v>61</v>
       </c>
       <c r="D5" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" s="3">
+        <v>100</v>
+      </c>
+      <c r="G5" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F5" s="3">
-        <v>70</v>
-      </c>
-      <c r="G5" s="3" t="s">
+      <c r="H5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I5" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="H5" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I5" s="3" t="s">
+      <c r="J5" s="3" t="s">
         <v>64</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="6">
@@ -1197,25 +1296,25 @@
         <v>66</v>
       </c>
       <c r="D6" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F6" s="3">
+        <v>96</v>
+      </c>
+      <c r="G6" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="E6" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F6" s="3">
+      <c r="H6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I6" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="G6" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>69</v>
-      </c>
       <c r="J6" s="3" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7">
@@ -1223,31 +1322,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F7" s="3">
+        <v>96</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I7" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F7" s="3">
-        <v>61</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>74</v>
-      </c>
       <c r="J7" s="3" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8">
@@ -1255,31 +1354,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F8" s="3">
-        <v>48</v>
+        <v>88</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>81</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9">
@@ -1287,31 +1386,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="C9" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F9" s="3">
         <v>83</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F9" s="3">
-        <v>47</v>
-      </c>
       <c r="G9" s="3" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
     </row>
     <row r="10">
@@ -1319,31 +1418,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>90</v>
+        <v>51</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F10" s="3">
-        <v>47</v>
+        <v>80</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
     </row>
     <row r="11">
@@ -1351,31 +1450,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>45</v>
+        <v>89</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F11" s="3">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>98</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12">
@@ -1383,31 +1482,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F12" s="3">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13">
@@ -1415,31 +1514,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>107</v>
+        <v>51</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F13" s="3">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
     </row>
     <row r="14">
@@ -1447,31 +1546,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>45</v>
+        <v>105</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F14" s="3">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>93</v>
+        <v>108</v>
       </c>
     </row>
     <row r="15">
@@ -1479,31 +1578,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>114</v>
+        <v>69</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F15" s="3">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>48</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -1511,31 +1610,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>76</v>
+        <v>114</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F16" s="3">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>81</v>
+        <v>119</v>
       </c>
     </row>
     <row r="17">
@@ -1543,31 +1642,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F17" s="3">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>48</v>
+        <v>124</v>
       </c>
     </row>
     <row r="18">
@@ -1575,31 +1674,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F18" s="3">
+        <v>46</v>
+      </c>
+      <c r="G18" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="H18" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I18" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="J18" s="3" t="s">
         <v>129</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F18" s="3">
-        <v>27</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="19">
@@ -1607,31 +1706,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F19" s="3">
+        <v>44</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I19" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="J19" s="3" t="s">
         <v>134</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F19" s="3">
-        <v>27</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="20">
@@ -1639,31 +1738,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F20" s="3">
+        <v>44</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I20" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="C20" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F20" s="3">
-        <v>24</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>143</v>
-      </c>
       <c r="J20" s="3" t="s">
-        <v>81</v>
+        <v>119</v>
       </c>
     </row>
     <row r="21">
@@ -1671,31 +1770,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F21" s="3">
+        <v>40</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="J21" s="3" t="s">
         <v>144</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F21" s="3">
-        <v>23</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="22">
@@ -1703,31 +1802,31 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F22" s="3">
+        <v>36</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="J22" s="3" t="s">
         <v>149</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F22" s="3">
-        <v>17</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="23">
@@ -1735,31 +1834,31 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>154</v>
+        <v>69</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>116</v>
+        <v>56</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F23" s="3">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>132</v>
+        <v>113</v>
       </c>
     </row>
     <row r="24">
@@ -1767,31 +1866,31 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>158</v>
+        <v>145</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>160</v>
+        <v>51</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F24" s="3">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>163</v>
+        <v>48</v>
       </c>
     </row>
     <row r="25">
@@ -1799,31 +1898,31 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>101</v>
+        <v>131</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F25" s="3">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>167</v>
+        <v>144</v>
       </c>
     </row>
     <row r="26">
@@ -1831,31 +1930,31 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>141</v>
+        <v>162</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F26" s="3">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>104</v>
+        <v>165</v>
       </c>
     </row>
   </sheetData>
@@ -1893,7 +1992,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="46" customWidth="1"/>
+    <col min="1" max="1" width="60" customWidth="1"/>
     <col min="2" max="2" width="37" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="31" customWidth="1"/>
@@ -1908,7 +2007,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>35</v>
@@ -1923,22 +2022,22 @@
         <v>38</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>40</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>42</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
     </row>
     <row r="2">
@@ -1952,7 +2051,7 @@
         <v>45</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E2" s="3">
         <v>100</v>
@@ -1961,7 +2060,7 @@
         <v>46</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>31</v>
@@ -1973,7 +2072,7 @@
         <v>48</v>
       </c>
       <c r="K2" s="3">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3">
@@ -1987,51 +2086,51 @@
         <v>51</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E3" s="3">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>52</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I3" s="3" t="s">
         <v>53</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="K3" s="3">
-        <v>42</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="C4" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>45</v>
-      </c>
       <c r="D4" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E4" s="3">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>57</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>31</v>
@@ -2043,7 +2142,7 @@
         <v>59</v>
       </c>
       <c r="K4" s="3">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -2054,31 +2153,31 @@
         <v>61</v>
       </c>
       <c r="C5" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" s="3">
+        <v>100</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E5" s="3">
-        <v>70</v>
-      </c>
-      <c r="F5" s="3" t="s">
+      <c r="G5" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I5" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="G5" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I5" s="3" t="s">
+      <c r="J5" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="J5" s="3" t="s">
-        <v>48</v>
-      </c>
       <c r="K5" s="3">
-        <v>18</v>
+        <v>88</v>
       </c>
     </row>
     <row r="6">
@@ -2089,728 +2188,728 @@
         <v>66</v>
       </c>
       <c r="C6" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" s="3">
+        <v>96</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E6" s="3">
+      <c r="G6" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I6" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="F6" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>69</v>
-      </c>
       <c r="J6" s="3" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="K6" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" s="3">
+        <v>96</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I7" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E7" s="3">
-        <v>61</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>74</v>
-      </c>
       <c r="J7" s="3" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="K7" s="3">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E8" s="3">
-        <v>48</v>
+        <v>88</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>81</v>
+        <v>59</v>
       </c>
       <c r="K8" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="B9" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E9" s="3">
         <v>83</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E9" s="3">
-        <v>47</v>
-      </c>
       <c r="F9" s="3" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="K9" s="3">
-        <v>8</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>90</v>
+        <v>51</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E10" s="3">
-        <v>47</v>
+        <v>80</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="K10" s="3">
-        <v>1</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>45</v>
+        <v>89</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E11" s="3">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>98</v>
+        <v>48</v>
       </c>
       <c r="K11" s="3">
-        <v>40</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E12" s="3">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="K12" s="3">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>107</v>
+        <v>51</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E13" s="3">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="K13" s="3">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>45</v>
+        <v>105</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E14" s="3">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="K14" s="3">
-        <v>1</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>114</v>
+        <v>69</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E15" s="3">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>48</v>
+        <v>113</v>
       </c>
       <c r="K15" s="3">
-        <v>18</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>76</v>
+        <v>114</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E16" s="3">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>81</v>
+        <v>119</v>
       </c>
       <c r="K16" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E17" s="3">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>48</v>
+        <v>124</v>
       </c>
       <c r="K17" s="3">
-        <v>18</v>
+        <v>41</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E18" s="3">
+        <v>46</v>
+      </c>
+      <c r="F18" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="G18" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I18" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="J18" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E18" s="3">
-        <v>27</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>132</v>
-      </c>
       <c r="K18" s="3">
-        <v>24</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E19" s="3">
+        <v>44</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I19" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="J19" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="C19" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E19" s="3">
-        <v>27</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>138</v>
-      </c>
       <c r="K19" s="3">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E20" s="3">
+        <v>44</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I20" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E20" s="3">
-        <v>24</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>143</v>
-      </c>
       <c r="J20" s="3" t="s">
-        <v>81</v>
+        <v>119</v>
       </c>
       <c r="K20" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E21" s="3">
+        <v>40</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="J21" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E21" s="3">
-        <v>23</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>148</v>
-      </c>
       <c r="K21" s="3">
-        <v>52</v>
+        <v>25</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E22" s="3">
+        <v>36</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="J22" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E22" s="3">
-        <v>17</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>153</v>
-      </c>
       <c r="K22" s="3">
-        <v>32</v>
+        <v>57</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>154</v>
+        <v>69</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>116</v>
+        <v>56</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E23" s="3">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>132</v>
+        <v>113</v>
       </c>
       <c r="K23" s="3">
-        <v>24</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>158</v>
+        <v>145</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>160</v>
+        <v>51</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E24" s="3">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>163</v>
+        <v>48</v>
       </c>
       <c r="K24" s="3">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>101</v>
+        <v>131</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E25" s="3">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>167</v>
+        <v>144</v>
       </c>
       <c r="K25" s="3">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>141</v>
+        <v>162</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E26" s="3">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>104</v>
+        <v>165</v>
       </c>
       <c r="K26" s="3">
         <v>12</v>
@@ -2818,109 +2917,424 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E27" s="3">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="K27" s="3">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>183</v>
+        <v>145</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>50</v>
+        <v>177</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>51</v>
+        <v>73</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E28" s="3">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="K28" s="3">
-        <v>67</v>
+        <v>20</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E29" s="3">
+        <v>24</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="K29" s="3">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="B30" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="C30" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="C29" s="3" t="s">
+      <c r="D30" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E30" s="3">
+        <v>23</v>
+      </c>
+      <c r="F30" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="D29" s="3" t="s">
+      <c r="G30" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I30" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="J30" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="K30" s="3">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E31" s="3">
+        <v>17</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I31" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="J31" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="K31" s="3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E32" s="3">
+        <v>12</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="K32" s="3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E33" s="3">
+        <v>12</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="K33" s="3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E34" s="3">
+        <v>10</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I34" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="J34" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="K34" s="3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E35" s="3">
+        <v>9</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="K35" s="3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E36" s="3">
+        <v>8</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I36" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="J36" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="K36" s="3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D37" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E29" s="3">
+      <c r="E37" s="3">
+        <v>4</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I37" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="J37" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="K37" s="3">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E38" s="3">
         <v>0</v>
       </c>
-      <c r="F29" s="3"/>
-      <c r="G29" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H29" s="3" t="s">
+      <c r="F38" s="3"/>
+      <c r="G38" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="H38" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="I29" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="K29" s="3">
-        <v>40</v>
+      <c r="I38" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="J38" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="K38" s="3">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K29"/>
+  <autoFilter ref="A1:K38"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1"/>
     <hyperlink ref="I3" r:id="rId2"/>
@@ -2950,6 +3364,15 @@
     <hyperlink ref="I27" r:id="rId26"/>
     <hyperlink ref="I28" r:id="rId27"/>
     <hyperlink ref="I29" r:id="rId28"/>
+    <hyperlink ref="I30" r:id="rId29"/>
+    <hyperlink ref="I31" r:id="rId30"/>
+    <hyperlink ref="I32" r:id="rId31"/>
+    <hyperlink ref="I33" r:id="rId32"/>
+    <hyperlink ref="I34" r:id="rId33"/>
+    <hyperlink ref="I35" r:id="rId34"/>
+    <hyperlink ref="I36" r:id="rId35"/>
+    <hyperlink ref="I37" r:id="rId36"/>
+    <hyperlink ref="I38" r:id="rId37"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -2957,11 +3380,11 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="23" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="24" customWidth="1"/>
+    <col min="1" max="1" width="31" customWidth="1"/>
+    <col min="2" max="2" width="25" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="5" max="5" width="60" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
@@ -2980,10 +3403,10 @@
         <v>38</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>42</v>
@@ -2991,31 +3414,103 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>164</v>
+        <v>54</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>165</v>
+        <v>55</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D2" s="3">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>156</v>
+        <v>57</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>166</v>
+        <v>58</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>167</v>
+        <v>59</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3" s="3">
+        <v>96</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" s="3">
+        <v>96</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" s="3">
+        <v>88</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>59</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G2"/>
+  <autoFilter ref="A1:G5"/>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1"/>
+    <hyperlink ref="F3" r:id="rId2"/>
+    <hyperlink ref="F4" r:id="rId3"/>
+    <hyperlink ref="F5" r:id="rId4"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -3030,178 +3525,178 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>191</v>
+        <v>225</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>192</v>
+        <v>226</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>193</v>
+        <v>227</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>194</v>
+        <v>228</v>
       </c>
       <c r="B2" s="3">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>195</v>
+        <v>229</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>156</v>
+        <v>230</v>
       </c>
       <c r="B3" s="3">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>196</v>
+        <v>231</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="B4" s="3">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>198</v>
+        <v>232</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>184</v>
+        <v>233</v>
       </c>
       <c r="B5" s="3">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>199</v>
+        <v>234</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>200</v>
+        <v>219</v>
       </c>
       <c r="B6" s="3">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>201</v>
+        <v>235</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>202</v>
+        <v>236</v>
       </c>
       <c r="B7" s="3">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>203</v>
+        <v>237</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>204</v>
+        <v>238</v>
       </c>
       <c r="B8" s="3">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>205</v>
+        <v>239</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>206</v>
+        <v>240</v>
       </c>
       <c r="B9" s="3">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>207</v>
+        <v>241</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>208</v>
+        <v>242</v>
       </c>
       <c r="B10" s="3">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>209</v>
+        <v>243</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>210</v>
+        <v>244</v>
       </c>
       <c r="B11" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>211</v>
+        <v>245</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>212</v>
+        <v>246</v>
       </c>
       <c r="B12" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>213</v>
+        <v>247</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>214</v>
+        <v>248</v>
       </c>
       <c r="B13" s="3">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>215</v>
+        <v>249</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>216</v>
+        <v>250</v>
       </c>
       <c r="B14" s="3">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>217</v>
+        <v>251</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>218</v>
+        <v>252</v>
       </c>
       <c r="B15" s="3">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>219</v>
+        <v>251</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>220</v>
+        <v>253</v>
       </c>
       <c r="B16" s="3">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>221</v>
+        <v>254</v>
       </c>
     </row>
   </sheetData>
@@ -3221,10 +3716,10 @@
         <v>37</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>222</v>
+        <v>255</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>223</v>
+        <v>256</v>
       </c>
     </row>
     <row r="2">
@@ -3232,10 +3727,10 @@
         <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>224</v>
+        <v>257</v>
       </c>
     </row>
     <row r="3">
@@ -3243,10 +3738,10 @@
         <v>26</v>
       </c>
       <c r="B3" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>225</v>
+        <v>258</v>
       </c>
     </row>
     <row r="4">
@@ -3254,10 +3749,10 @@
         <v>27</v>
       </c>
       <c r="B4" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>226</v>
+        <v>259</v>
       </c>
     </row>
     <row r="5">
@@ -3268,7 +3763,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>227</v>
+        <v>260</v>
       </c>
     </row>
     <row r="6">
@@ -3279,7 +3774,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>228</v>
+        <v>261</v>
       </c>
     </row>
   </sheetData>
@@ -3300,13 +3795,13 @@
         <v>40</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>229</v>
+        <v>262</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>230</v>
+        <v>263</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>231</v>
+        <v>264</v>
       </c>
     </row>
     <row r="2">
@@ -3317,7 +3812,7 @@
         <v>5</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>232</v>
+        <v>265</v>
       </c>
       <c r="D2" s="3"/>
     </row>
@@ -3326,22 +3821,22 @@
         <v>31</v>
       </c>
       <c r="B3" s="3">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>232</v>
+        <v>265</v>
       </c>
       <c r="D3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>233</v>
+        <v>266</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>232</v>
+        <v>265</v>
       </c>
       <c r="D4" s="3"/>
     </row>

--- a/reports/devops-juniors-israel-2026-W37.xlsx
+++ b/reports/devops-juniors-israel-2026-W37.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="267">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="338">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-08T11:09:39</t>
+    <t xml:space="preserve">2026-09-09T11:14:16</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -91,19 +91,22 @@
     <t xml:space="preserve">By bucket</t>
   </si>
   <si>
+    <t xml:space="preserve">Help Desk / IT Support</t>
+  </si>
+  <si>
     <t xml:space="preserve">SysAdmin / NOC</t>
   </si>
   <si>
-    <t xml:space="preserve">Help Desk / IT Support</t>
-  </si>
-  <si>
     <t xml:space="preserve">Trainee / Bootcamp Grad</t>
   </si>
   <si>
+    <t xml:space="preserve">Junior SysAdmin / Linux</t>
+  </si>
+  <si>
     <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
   </si>
   <si>
-    <t xml:space="preserve">Junior SysAdmin / Linux</t>
+    <t xml:space="preserve">Junior DevOps</t>
   </si>
   <si>
     <t xml:space="preserve">By source</t>
@@ -163,325 +166,403 @@
     <t xml:space="preserve">2026-08-20</t>
   </si>
   <si>
+    <t xml:space="preserve">DevOps &amp; Cloud Infrastructure Intern</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-infrastructure-intern-at-f5-4464650168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-09</t>
+  </si>
+  <si>
     <t xml:space="preserve">NOC Team Leader</t>
   </si>
   <si>
     <t xml:space="preserve">Rapyd</t>
   </si>
   <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-team-leader-at-rapyd-4428470164</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calanit by one</t>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SuperCom (NASDAQ: SPCB)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, Cloud (any), CI/CD, Git, Networking, Monitoring, Databases, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-supercom-nasdaq-spcb-4462293466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">comblack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), CI/CD, Git, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-comblack-4464346266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator (Nutanix Expert)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">peax dorcom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, AWS, Azure, GCP, Cloud (any), Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-nutanix-expert-at-peax-dorcom-4459918624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel - Raanana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4850412101?gh_jid=4850412101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Technical Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iGATES - INFORMATION GATES Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-operations-engineer-at-igates-information-gates-ltd-4452212223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Engineer Student, SPIV team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amazon Web Services (AWS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, CI/CD, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-student-spiv-team-at-amazon-web-services-aws-4456348779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Production Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Torq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6179167004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer (NOC / Tier 1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kela Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-noc-tier-1-at-kela-technologies-4461059776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Computer System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Camtek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Migdal HaEmek, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/computer-system-engineer-at-camtek-4432772061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONTROP Precision Technologies Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Networking, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-controp-precision-technologies-ltd-4460943847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upwind Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Networking, Monitoring, Databases, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-upwind-security-4460871956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lumana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-lumana-4463708633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist – MENTEE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobileye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Cloud (any), Terraform/IaC, Networking, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-%E2%80%93-mentee-at-mobileye-4445729205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Cloud Security Engineer (Entry-Level)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OnCloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cloud-security-engineer-entry-level-at-oncloud-4456904380</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TytoCare</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-tytocare-4461579939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator - 243425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experis Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-243425-at-experis-israel-4461821675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Operations &amp; Security Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PointFive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Cloud (any), Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-security-specialist-at-pointfive-4426311043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Engineering INTERN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Cloud (any), CI/CD, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineering-intern-at-microsoft-4451071541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raft Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4433796227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Enterprise Systems Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cross River</t>
+  </si>
+  <si>
+    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Azure, Cloud (any), Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-enterprise-systems-support-engineer-at-cross-river-4464614783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yael Korentec Technologies</t>
   </si>
   <si>
     <t xml:space="preserve">North District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-calanit-by-one-4464446970</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator / DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SuperCom (NASDAQ: SPCB)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, Cloud (any), CI/CD, Git, Networking, Monitoring, Databases, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-devops-at-supercom-nasdaq-spcb-4464376479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-supercom-nasdaq-spcb-4462293466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">comblack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), CI/CD, Git, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-comblack-4464346266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel - Raanana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4850412101?gh_jid=4850412101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Technical Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iGATES - INFORMATION GATES Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-operations-engineer-at-igates-information-gates-ltd-4452212223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Engineer Student, SPIV team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Amazon Web Services (AWS)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, CI/CD, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-student-spiv-team-at-amazon-web-services-aws-4456348779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Production Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Torq</t>
-  </si>
-  <si>
-    <t xml:space="preserve">israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6179167004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer (NOC / Tier 1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kela Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-noc-tier-1-at-kela-technologies-4461059776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Computer System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Camtek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Migdal HaEmek, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/computer-system-engineer-at-camtek-4432772061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CONTROP Precision Technologies Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Networking, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-controp-precision-technologies-ltd-4460943847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lumana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-lumana-4463708633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist – MENTEE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mobileye</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Cloud (any), Terraform/IaC, Networking, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-%E2%80%93-mentee-at-mobileye-4445729205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Cloud Security Engineer (Entry-Level)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OnCloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cloud-security-engineer-entry-level-at-oncloud-4456904380</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TytoCare</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-tytocare-4461579939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator - 243425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experis Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-243425-at-experis-israel-4461821675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Operations &amp; Security Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PointFive</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Cloud (any), Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-security-specialist-at-pointfive-4426311043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raft Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4433796227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yael Korentec Technologies</t>
-  </si>
-  <si>
     <t xml:space="preserve">Linux, Networking, Virtualization, Active Directory, Windows Server, Troubleshooting</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-yael-korentec-technologies-4462122131</t>
   </si>
   <si>
-    <t xml:space="preserve">Gini-Apps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Networking, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-gini-apps-4440026223</t>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs JD Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Communication System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ceva, Inc.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/communication-system-engineer-at-ceva-inc-4459357209</t>
   </si>
   <si>
     <t xml:space="preserve">Support Engineer</t>
@@ -496,165 +577,204 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-fetcherr-4449296509</t>
   </si>
   <si>
-    <t xml:space="preserve">Junior Field Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mornex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-field-support-engineer-at-mornex-4457946363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs JD Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days Open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator (24/7 Shift-Based)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">evoke</t>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Systems Engineer 2, Technical Operations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oracle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineer-2-technical-operations-at-oracle-4441078871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Center IT Technician - Masmiya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nebius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-masmiya-at-nebius-4437672340</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Center IT Technician - Beit Shemesh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-beit-shemesh-at-nebius-4437673265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk &amp; Field Service Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stratasys</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-field-service-technician-at-stratasys-4461321939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Engineer - Entry Level</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check Point Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-entry-level-at-check-point-software-4441459886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">איש/אשת תמיכה טכנית ו -Helpdesk 2+בפתח תקווה</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arad Tech - Technology, Engineering &amp; AI Recruitment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Networking, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%90%D7%99%D7%A9-%D7%90%D7%A9%D7%AA-%D7%AA%D7%9E%D7%99%D7%9B%D7%94-%D7%98%D7%9B%D7%A0%D7%99%D7%AA-%D7%95-helpdesk-2%2B%D7%91%D7%A4%D7%AA%D7%97-%D7%AA%D7%A7%D7%95%D7%95%D7%94-at-arad-tech-technology-engineering-ai-recruitment-4440622529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lab Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harmonic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/lab-support-engineer-at-harmonic-4448547160</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Service Desk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tata Consultancy Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/service-desk-specialist-at-tata-consultancy-services-4463224629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kaltura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-kaltura-4455279134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-tata-consultancy-services-4459788315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estonia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-technician-at-comblack-4464328677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-kaltura-4460895402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COM-C-TECH LTD</t>
   </si>
   <si>
     <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux, Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-24-7-shift-based-at-evoke-4462157700</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Systems Engineer 2, Technical Operations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oracle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineer-2-technical-operations-at-oracle-4441078871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Center IT Technician - Masmiya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nebius</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-masmiya-at-nebius-4437672340</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lab Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harmonic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/lab-support-engineer-at-harmonic-4448547160</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tata Consultancy Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-tata-consultancy-services-4459788315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WaveBL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc%0Aisrael-at-wavebl-4443917908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optimove</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estonia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COM-C-TECH LTD</t>
-  </si>
-  <si>
     <t xml:space="preserve">Active Directory, Windows Server</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-administrator-at-com-c-tech-ltd-4457234117</t>
   </si>
   <si>
+    <t xml:space="preserve">Cloud Platform Engineer - Student (Java)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-engineer-student-java-at-sap-4457493270</t>
+  </si>
+  <si>
     <t xml:space="preserve">NOC Engineer- Student Position</t>
   </si>
   <si>
@@ -670,6 +790,51 @@
     <t xml:space="preserve">2026-08-21</t>
   </si>
   <si>
+    <t xml:space="preserve">AudioCodes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-audiocodes-4454240269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Support Specialist (37425)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-support-specialist-37425-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4464324940</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-technician-at-abra-4454760617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Engineer (Tier 2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HCLTech</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-engineer-tier-2-at-hcltech-4445746731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tier I Technical Support Specialist — Smart Cooler Vending</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jobgether</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/tier-i-technical-support-specialist-%E2%80%94-smart-cooler-vending-at-jobgether-4463227567</t>
+  </si>
+  <si>
     <t xml:space="preserve">Employer Branding Student (Temporary )</t>
   </si>
   <si>
@@ -679,6 +844,54 @@
     <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4912601101?gh_jid=4912601101</t>
   </si>
   <si>
+    <t xml:space="preserve">Junior Power Control System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SolarEdge Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-power-control-system-engineer-at-solaredge-technologies-4438264844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk &amp; Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tipuli Tech</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-support-specialist-at-tipuli-tech-4447121790</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Desktop Support Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Impact Networks Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Be'er Sheva, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/desktop-support-technician-at-impact-networks-group-4464458660</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk (36409)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-36409-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4464346260</t>
+  </si>
+  <si>
     <t xml:space="preserve">Working Student, Legal (German-speaking)</t>
   </si>
   <si>
@@ -700,18 +913,15 @@
     <t xml:space="preserve">What to learn / where to start</t>
   </si>
   <si>
-    <t xml:space="preserve">Troubleshooting</t>
-  </si>
-  <si>
     <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
   </si>
   <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
   </si>
   <si>
+    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
+  </si>
+  <si>
     <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
   </si>
   <si>
@@ -721,9 +931,6 @@
     <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
   </si>
   <si>
-    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
-  </si>
-  <si>
     <t xml:space="preserve">Automation</t>
   </si>
   <si>
@@ -736,6 +943,18 @@
     <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
   </si>
   <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
+  </si>
+  <si>
     <t xml:space="preserve">Python</t>
   </si>
   <si>
@@ -748,37 +967,28 @@
     <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
   </si>
   <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
-  </si>
-  <si>
     <t xml:space="preserve">CI/CD</t>
   </si>
   <si>
     <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
   </si>
   <si>
-    <t xml:space="preserve">Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
-  </si>
-  <si>
     <t xml:space="preserve">Virtualization</t>
   </si>
   <si>
     <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
   </si>
   <si>
-    <t xml:space="preserve">Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Git</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pro Git book (free online) + create a learning repo</t>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free Docker Get Started tutorial + build 3 home-lab containers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kubernetes.io tutorials → minikube on laptop → KCNA cert</t>
   </si>
   <si>
     <t xml:space="preserve">Count</t>
@@ -787,19 +997,22 @@
     <t xml:space="preserve">Pivot path advice</t>
   </si>
   <si>
+    <t xml:space="preserve">Tier 1/2 → SysAdmin → Junior DevOps. ~24 month path.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Already in IT — strengthen Linux + automation → apply to DevOps in 12-18mo.</t>
   </si>
   <si>
-    <t xml:space="preserve">Tier 1/2 → SysAdmin → Junior DevOps. ~24 month path.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cyclical — surge after bootcamp graduations (Aug/Feb).</t>
   </si>
   <si>
+    <t xml:space="preserve">12-18 months → Junior DevOps. Strengthen Linux + Python + AWS.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Often paired with on-call. Strong learning track.</t>
   </si>
   <si>
-    <t xml:space="preserve">12-18 months → Junior DevOps. Strengthen Linux + Python + AWS.</t>
+    <t xml:space="preserve">Direct DevOps role — apply aggressively. Rare and competitive.</t>
   </si>
   <si>
     <t xml:space="preserve">Jobs</t>
@@ -939,7 +1152,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>37</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7">
@@ -947,7 +1160,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
@@ -955,7 +1168,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9">
@@ -963,7 +1176,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="10">
@@ -1045,7 +1258,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="22">
@@ -1053,7 +1266,7 @@
         <v>26</v>
       </c>
       <c r="B22" s="3">
-        <v>8</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23">
@@ -1061,7 +1274,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24">
@@ -1069,7 +1282,7 @@
         <v>28</v>
       </c>
       <c r="B24" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1081,28 +1294,36 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3"/>
-      <c r="B26" s="3"/>
+      <c r="A26" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B26" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="s">
-        <v>30</v>
-      </c>
+      <c r="A27" s="3"/>
       <c r="B27" s="3"/>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B28" s="3">
-        <v>32</v>
-      </c>
+      <c r="B28" s="3"/>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
         <v>32</v>
       </c>
       <c r="B29" s="3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B30" s="3">
         <v>5</v>
       </c>
     </row>
@@ -1116,7 +1337,7 @@
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
     <col min="3" max="3" width="37" customWidth="1"/>
-    <col min="4" max="4" width="42" customWidth="1"/>
+    <col min="4" max="4" width="44" customWidth="1"/>
     <col min="5" max="5" width="31" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
     <col min="7" max="7" width="60" customWidth="1"/>
@@ -1127,34 +1348,34 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2">
@@ -1162,13 +1383,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>27</v>
@@ -1177,16 +1398,16 @@
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3">
@@ -1194,31 +1415,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4">
@@ -1226,31 +1447,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F4" s="3">
         <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5">
@@ -1264,10 +1485,10 @@
         <v>61</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F5" s="3">
         <v>100</v>
@@ -1276,7 +1497,7 @@
         <v>62</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I5" s="3" t="s">
         <v>63</v>
@@ -1296,25 +1517,25 @@
         <v>66</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F6" s="3">
         <v>96</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="7">
@@ -1322,31 +1543,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="D7" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" s="3">
+        <v>88</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="J7" s="3" t="s">
         <v>70</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F7" s="3">
-        <v>96</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="8">
@@ -1354,31 +1575,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F8" s="3">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>59</v>
+        <v>79</v>
       </c>
     </row>
     <row r="9">
@@ -1386,13 +1607,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>27</v>
@@ -1401,16 +1622,16 @@
         <v>83</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
     </row>
     <row r="10">
@@ -1418,31 +1639,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F10" s="3">
         <v>80</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
     </row>
     <row r="11">
@@ -1450,13 +1671,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>27</v>
@@ -1465,16 +1686,16 @@
         <v>70</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12">
@@ -1482,31 +1703,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F12" s="3">
         <v>68</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
     </row>
     <row r="13">
@@ -1514,31 +1735,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F13" s="3">
         <v>61</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
     </row>
     <row r="14">
@@ -1546,31 +1767,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F14" s="3">
         <v>56</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
     <row r="15">
@@ -1578,31 +1799,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F15" s="3">
         <v>48</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>113</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -1610,31 +1831,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F16" s="3">
         <v>47</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="17">
@@ -1642,31 +1863,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>51</v>
+        <v>125</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F17" s="3">
         <v>47</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
     </row>
     <row r="18">
@@ -1674,31 +1895,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>73</v>
+        <v>52</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F18" s="3">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
     </row>
     <row r="19">
@@ -1706,31 +1927,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>69</v>
+        <v>134</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>131</v>
+        <v>72</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F19" s="3">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
     </row>
     <row r="20">
@@ -1738,31 +1959,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>135</v>
+        <v>65</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F20" s="3">
         <v>44</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>119</v>
+        <v>143</v>
       </c>
     </row>
     <row r="21">
@@ -1770,31 +1991,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>70</v>
+        <v>146</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F21" s="3">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
     </row>
     <row r="22">
@@ -1802,31 +2023,31 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F22" s="3">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
     </row>
     <row r="23">
@@ -1834,31 +2055,31 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>69</v>
+        <v>154</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>56</v>
+        <v>156</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F23" s="3">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>113</v>
+        <v>49</v>
       </c>
     </row>
     <row r="24">
@@ -1866,31 +2087,31 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>145</v>
+        <v>159</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F24" s="3">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>48</v>
+        <v>163</v>
       </c>
     </row>
     <row r="25">
@@ -1898,31 +2119,31 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>131</v>
+        <v>166</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F25" s="3">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>144</v>
+        <v>55</v>
       </c>
     </row>
     <row r="26">
@@ -1930,31 +2151,31 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>160</v>
+        <v>65</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F26" s="3">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>165</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -1993,8 +2214,8 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="37" customWidth="1"/>
-    <col min="3" max="3" width="42" customWidth="1"/>
+    <col min="2" max="2" width="54" customWidth="1"/>
+    <col min="3" max="3" width="44" customWidth="1"/>
     <col min="4" max="4" width="31" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
@@ -2007,48 +2228,48 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>27</v>
@@ -2057,92 +2278,92 @@
         <v>100</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K2" s="3">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E3" s="3">
         <v>100</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="K3" s="3">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E4" s="3">
         <v>100</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="K4" s="3">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5">
@@ -2153,10 +2374,10 @@
         <v>61</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E5" s="3">
         <v>100</v>
@@ -2165,10 +2386,10 @@
         <v>62</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I5" s="3" t="s">
         <v>63</v>
@@ -2177,7 +2398,7 @@
         <v>64</v>
       </c>
       <c r="K5" s="3">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="6">
@@ -2188,112 +2409,112 @@
         <v>66</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E6" s="3">
         <v>96</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="K6" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="C7" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" s="3">
+        <v>88</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="J7" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E7" s="3">
-        <v>96</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>59</v>
-      </c>
       <c r="K7" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E8" s="3">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>59</v>
+        <v>79</v>
       </c>
       <c r="K8" s="3">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>27</v>
@@ -2302,68 +2523,68 @@
         <v>83</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="K9" s="3">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E10" s="3">
         <v>80</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="K10" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>27</v>
@@ -2372,969 +2593,1599 @@
         <v>70</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K11" s="3">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E12" s="3">
         <v>68</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="K12" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E13" s="3">
         <v>61</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="K13" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E14" s="3">
         <v>56</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="K14" s="3">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E15" s="3">
         <v>48</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>113</v>
+        <v>79</v>
       </c>
       <c r="K15" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E16" s="3">
         <v>47</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="K16" s="3">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>51</v>
+        <v>125</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E17" s="3">
         <v>47</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="K17" s="3">
-        <v>41</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>73</v>
+        <v>52</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E18" s="3">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="K18" s="3">
-        <v>13</v>
+        <v>42</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>69</v>
+        <v>134</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>131</v>
+        <v>72</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E19" s="3">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="K19" s="3">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>135</v>
+        <v>65</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E20" s="3">
         <v>44</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>119</v>
+        <v>143</v>
       </c>
       <c r="K20" s="3">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>70</v>
+        <v>146</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E21" s="3">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="K21" s="3">
-        <v>25</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E22" s="3">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="K22" s="3">
-        <v>57</v>
+        <v>26</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>69</v>
+        <v>154</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>56</v>
+        <v>156</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E23" s="3">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>113</v>
+        <v>49</v>
       </c>
       <c r="K23" s="3">
-        <v>6</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>145</v>
+        <v>159</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E24" s="3">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>48</v>
+        <v>163</v>
       </c>
       <c r="K24" s="3">
-        <v>19</v>
+        <v>58</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>131</v>
+        <v>166</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E25" s="3">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>144</v>
+        <v>55</v>
       </c>
       <c r="K25" s="3">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>160</v>
+        <v>65</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E26" s="3">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>165</v>
+        <v>79</v>
       </c>
       <c r="K26" s="3">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>174</v>
+        <v>46</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E27" s="3">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="K27" s="3">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>145</v>
+        <v>183</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>73</v>
+        <v>140</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E28" s="3">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>180</v>
+        <v>153</v>
       </c>
       <c r="K28" s="3">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>181</v>
+        <v>159</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>137</v>
+        <v>72</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E29" s="3">
         <v>24</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="K29" s="3">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>188</v>
+        <v>146</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E30" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="K30" s="3">
-        <v>53</v>
+        <v>24</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>116</v>
+        <v>156</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E31" s="3">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="K31" s="3">
-        <v>33</v>
+        <v>54</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>145</v>
+        <v>201</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>197</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>137</v>
+        <v>156</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E32" s="3">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>198</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>134</v>
+        <v>153</v>
       </c>
       <c r="K32" s="3">
-        <v>7</v>
+        <v>26</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>188</v>
+        <v>205</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E33" s="3">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>144</v>
+        <v>55</v>
       </c>
       <c r="K33" s="3">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>206</v>
+        <v>52</v>
       </c>
       <c r="D34" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E34" s="3">
+        <v>20</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I34" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="J34" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="K34" s="3">
         <v>26</v>
-      </c>
-      <c r="E34" s="3">
-        <v>10</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="G34" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="H34" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I34" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="J34" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="K34" s="3">
-        <v>15</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>174</v>
+        <v>146</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E35" s="3">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>129</v>
+        <v>216</v>
       </c>
       <c r="K35" s="3">
-        <v>13</v>
+        <v>55</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E36" s="3">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="K36" s="3">
-        <v>18</v>
+        <v>34</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>77</v>
+        <v>223</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E37" s="3">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="H37" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>108</v>
+        <v>55</v>
       </c>
       <c r="K37" s="3">
-        <v>68</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="C38" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E38" s="3">
+        <v>13</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I38" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="J38" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="K38" s="3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="B39" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="D38" s="3" t="s">
+      <c r="C39" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E39" s="3">
+        <v>12</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I39" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="J39" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="K39" s="3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E40" s="3">
+        <v>10</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I40" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="J40" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="K40" s="3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E41" s="3">
+        <v>10</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="J41" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="K41" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E42" s="3">
+        <v>10</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I42" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="J42" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="K42" s="3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E43" s="3">
+        <v>9</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="K43" s="3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D44" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E38" s="3">
+      <c r="E44" s="3">
+        <v>8</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="K44" s="3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E45" s="3">
+        <v>8</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="K45" s="3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E46" s="3">
+        <v>6</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I46" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="J46" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="K46" s="3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E47" s="3">
+        <v>6</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="K47" s="3">
         <v>0</v>
       </c>
-      <c r="F38" s="3"/>
-      <c r="G38" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="H38" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I38" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="J38" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="K38" s="3">
-        <v>41</v>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E48" s="3">
+        <v>6</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="J48" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="K48" s="3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E49" s="3">
+        <v>6</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I49" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="J49" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="K49" s="3">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E50" s="3">
+        <v>6</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="G50" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H50" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I50" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="J50" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="K50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E51" s="3">
+        <v>4</v>
+      </c>
+      <c r="F51" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="G51" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H51" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I51" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="J51" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="K51" s="3">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E52" s="3">
+        <v>4</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="K52" s="3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E53" s="3">
+        <v>3</v>
+      </c>
+      <c r="F53" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="G53" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H53" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I53" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="J53" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="K53" s="3">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E54" s="3">
+        <v>3</v>
+      </c>
+      <c r="F54" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I54" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="J54" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="K54" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E55" s="3">
+        <v>3</v>
+      </c>
+      <c r="F55" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="G55" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H55" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I55" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="J55" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="K55" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E56" s="3">
+        <v>0</v>
+      </c>
+      <c r="F56" s="3"/>
+      <c r="G56" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H56" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I56" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="J56" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="K56" s="3">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K38"/>
+  <autoFilter ref="A1:K56"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1"/>
     <hyperlink ref="I3" r:id="rId2"/>
@@ -3373,6 +4224,24 @@
     <hyperlink ref="I36" r:id="rId35"/>
     <hyperlink ref="I37" r:id="rId36"/>
     <hyperlink ref="I38" r:id="rId37"/>
+    <hyperlink ref="I39" r:id="rId38"/>
+    <hyperlink ref="I40" r:id="rId39"/>
+    <hyperlink ref="I41" r:id="rId40"/>
+    <hyperlink ref="I42" r:id="rId41"/>
+    <hyperlink ref="I43" r:id="rId42"/>
+    <hyperlink ref="I44" r:id="rId43"/>
+    <hyperlink ref="I45" r:id="rId44"/>
+    <hyperlink ref="I46" r:id="rId45"/>
+    <hyperlink ref="I47" r:id="rId46"/>
+    <hyperlink ref="I48" r:id="rId47"/>
+    <hyperlink ref="I49" r:id="rId48"/>
+    <hyperlink ref="I50" r:id="rId49"/>
+    <hyperlink ref="I51" r:id="rId50"/>
+    <hyperlink ref="I52" r:id="rId51"/>
+    <hyperlink ref="I53" r:id="rId52"/>
+    <hyperlink ref="I54" r:id="rId53"/>
+    <hyperlink ref="I55" r:id="rId54"/>
+    <hyperlink ref="I56" r:id="rId55"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -3380,9 +4249,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="31" customWidth="1"/>
-    <col min="2" max="2" width="25" customWidth="1"/>
-    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="1" max="1" width="60" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="3" max="3" width="24" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="60" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
@@ -3391,126 +4260,222 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D2" s="3">
         <v>100</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>65</v>
+        <v>164</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>66</v>
+        <v>165</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D3" s="3">
-        <v>96</v>
+        <v>34</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>67</v>
+        <v>167</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>68</v>
+        <v>168</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>69</v>
+        <v>203</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>66</v>
+        <v>204</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D4" s="3">
-        <v>96</v>
+        <v>20</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>67</v>
+        <v>206</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>71</v>
+        <v>207</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>60</v>
+        <v>222</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>72</v>
+        <v>223</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D5" s="3">
-        <v>88</v>
+        <v>17</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>74</v>
+        <v>224</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>75</v>
+        <v>225</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>59</v>
+        <v>55</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="3">
+        <v>6</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" s="3">
+        <v>6</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" s="3">
+        <v>3</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9" s="3">
+        <v>3</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>55</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G5"/>
+  <autoFilter ref="A1:G9"/>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1"/>
     <hyperlink ref="F3" r:id="rId2"/>
     <hyperlink ref="F4" r:id="rId3"/>
     <hyperlink ref="F5" r:id="rId4"/>
+    <hyperlink ref="F6" r:id="rId5"/>
+    <hyperlink ref="F7" r:id="rId6"/>
+    <hyperlink ref="F8" r:id="rId7"/>
+    <hyperlink ref="F9" r:id="rId8"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -3525,178 +4490,178 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>225</v>
+        <v>296</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>226</v>
+        <v>297</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>227</v>
+        <v>298</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>228</v>
+        <v>278</v>
       </c>
       <c r="B2" s="3">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>229</v>
+        <v>299</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>230</v>
+        <v>288</v>
       </c>
       <c r="B3" s="3">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>231</v>
+        <v>300</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>202</v>
+        <v>274</v>
       </c>
       <c r="B4" s="3">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>232</v>
+        <v>301</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="B5" s="3">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>234</v>
+        <v>302</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>219</v>
+        <v>303</v>
       </c>
       <c r="B6" s="3">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>235</v>
+        <v>304</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>236</v>
+        <v>305</v>
       </c>
       <c r="B7" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>237</v>
+        <v>306</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>238</v>
+        <v>307</v>
       </c>
       <c r="B8" s="3">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>239</v>
+        <v>308</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>240</v>
+        <v>309</v>
       </c>
       <c r="B9" s="3">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>241</v>
+        <v>310</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>242</v>
+        <v>311</v>
       </c>
       <c r="B10" s="3">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>243</v>
+        <v>312</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>244</v>
+        <v>313</v>
       </c>
       <c r="B11" s="3">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>245</v>
+        <v>314</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>246</v>
+        <v>315</v>
       </c>
       <c r="B12" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>247</v>
+        <v>316</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>248</v>
+        <v>317</v>
       </c>
       <c r="B13" s="3">
         <v>10</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>249</v>
+        <v>318</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>250</v>
+        <v>319</v>
       </c>
       <c r="B14" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>251</v>
+        <v>320</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>252</v>
+        <v>321</v>
       </c>
       <c r="B15" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>251</v>
+        <v>322</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>253</v>
+        <v>323</v>
       </c>
       <c r="B16" s="3">
         <v>7</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>254</v>
+        <v>324</v>
       </c>
     </row>
   </sheetData>
@@ -3713,13 +4678,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>255</v>
+        <v>325</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>256</v>
+        <v>326</v>
       </c>
     </row>
     <row r="2">
@@ -3727,10 +4692,10 @@
         <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>257</v>
+        <v>327</v>
       </c>
     </row>
     <row r="3">
@@ -3738,10 +4703,10 @@
         <v>26</v>
       </c>
       <c r="B3" s="3">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>258</v>
+        <v>328</v>
       </c>
     </row>
     <row r="4">
@@ -3749,10 +4714,10 @@
         <v>27</v>
       </c>
       <c r="B4" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>259</v>
+        <v>329</v>
       </c>
     </row>
     <row r="5">
@@ -3760,10 +4725,10 @@
         <v>28</v>
       </c>
       <c r="B5" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>260</v>
+        <v>330</v>
       </c>
     </row>
     <row r="6">
@@ -3774,7 +4739,18 @@
         <v>1</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>261</v>
+        <v>331</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" s="3">
+        <v>1</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>332</v>
       </c>
     </row>
   </sheetData>
@@ -3792,51 +4768,51 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>262</v>
+        <v>333</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>263</v>
+        <v>334</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>264</v>
+        <v>335</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B2" s="3">
         <v>5</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>265</v>
+        <v>336</v>
       </c>
       <c r="D2" s="3"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B3" s="3">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>265</v>
+        <v>336</v>
       </c>
       <c r="D3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>266</v>
+        <v>337</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>265</v>
+        <v>336</v>
       </c>
       <c r="D4" s="3"/>
     </row>

--- a/reports/devops-juniors-israel-2026-W37.xlsx
+++ b/reports/devops-juniors-israel-2026-W37.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="338">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="294">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09T11:14:16</t>
+    <t xml:space="preserve">2026-09-10T11:10:19</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -91,12 +91,12 @@
     <t xml:space="preserve">By bucket</t>
   </si>
   <si>
+    <t xml:space="preserve">SysAdmin / NOC</t>
+  </si>
+  <si>
     <t xml:space="preserve">Help Desk / IT Support</t>
   </si>
   <si>
-    <t xml:space="preserve">SysAdmin / NOC</t>
-  </si>
-  <si>
     <t xml:space="preserve">Trainee / Bootcamp Grad</t>
   </si>
   <si>
@@ -118,6 +118,9 @@
     <t xml:space="preserve">greenhouse</t>
   </si>
   <si>
+    <t xml:space="preserve">remoteok</t>
+  </si>
+  <si>
     <t xml:space="preserve">Rank</t>
   </si>
   <si>
@@ -184,18 +187,6 @@
     <t xml:space="preserve">2026-09-09</t>
   </si>
   <si>
-    <t xml:space="preserve">NOC Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rapyd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-team-leader-at-rapyd-4428470164</t>
-  </si>
-  <si>
     <t xml:space="preserve">System Engineer</t>
   </si>
   <si>
@@ -229,732 +220,615 @@
     <t xml:space="preserve">2026-09-08</t>
   </si>
   <si>
-    <t xml:space="preserve">comblack</t>
+    <t xml:space="preserve">System Administrator (Nutanix Expert)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">peax dorcom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, AWS, Azure, GCP, Cloud (any), Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-nutanix-expert-at-peax-dorcom-4459918624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel - Raanana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4850412101?gh_jid=4850412101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Technical Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iGATES - INFORMATION GATES Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-operations-engineer-at-igates-information-gates-ltd-4452212223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Production Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Torq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6179167004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer (NOC / Tier 1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kela Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-noc-tier-1-at-kela-technologies-4461059776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONTROP Precision Technologies Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Networking, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-controp-precision-technologies-ltd-4460943847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upwind Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Networking, Monitoring, Databases, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-upwind-security-4460871956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lumana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-lumana-4463708633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Cloud Security Engineer (Entry-Level)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OnCloud</t>
   </si>
   <si>
     <t xml:space="preserve">Center District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), CI/CD, Git, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-comblack-4464346266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator (Nutanix Expert)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">peax dorcom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, AWS, Azure, GCP, Cloud (any), Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-nutanix-expert-at-peax-dorcom-4459918624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel - Raanana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4850412101?gh_jid=4850412101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Technical Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iGATES - INFORMATION GATES Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-operations-engineer-at-igates-information-gates-ltd-4452212223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Engineer Student, SPIV team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Amazon Web Services (AWS)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, CI/CD, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-student-spiv-team-at-amazon-web-services-aws-4456348779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Production Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Torq</t>
-  </si>
-  <si>
-    <t xml:space="preserve">israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6179167004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer (NOC / Tier 1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kela Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-noc-tier-1-at-kela-technologies-4461059776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Computer System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Camtek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Migdal HaEmek, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/computer-system-engineer-at-camtek-4432772061</t>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cloud-security-engineer-entry-level-at-oncloud-4456904380</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operations Analyst Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel - Tel Aviv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/forter/jobs/8759588002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TytoCare</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-tytocare-4461579939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator - 243425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experis Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-243425-at-experis-israel-4461821675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Engineering INTERN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Cloud (any), CI/CD, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineering-intern-at-microsoft-4451071541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yael Korentec Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Virtualization, Active Directory, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-yael-korentec-technologies-4462122131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gini-Apps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Networking, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-gini-apps-4440026223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Communication System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ceva, Inc.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/communication-system-engineer-at-ceva-inc-4459357209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Field Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mornex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-field-support-engineer-at-mornex-4457946363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator (24/7 Shift-Based)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">evoke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-24-7-shift-based-at-evoke-4462157700</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Systems Engineer 2, Technical Operations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oracle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineer-2-technical-operations-at-oracle-4444274357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk &amp; Field Service Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stratasys</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-field-service-technician-at-stratasys-4461321939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs JD Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Service Desk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tata Consultancy Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/service-desk-specialist-at-tata-consultancy-services-4463224629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kaltura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-kaltura-4455279134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WaveBL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc%0A%09%09%09%09%09%09%09%09%09%0A%09%09%09%09%09%09%09%09%0A%09%09%09%09%09%09%09%09%09%09israel-at-wavebl-4443917908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estonia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-kaltura-4460895402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COM-C-TECH LTD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory, Windows Server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-administrator-at-com-c-tech-ltd-4457234117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Platform Engineer - Student (Java)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-engineer-student-java-at-sap-4457493270</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PassportCard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-at-passportcard-4458103759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NBS-HR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shoham, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-nbs-hr-4463014591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AudioCodes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-audiocodes-4454240269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Employer Branding Student (Temporary )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4912601101?gh_jid=4912601101</t>
   </si>
   <si>
     <t xml:space="preserve">2026-07-02</t>
   </si>
   <si>
-    <t xml:space="preserve">CONTROP Precision Technologies Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Networking, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-controp-precision-technologies-ltd-4460943847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upwind Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Networking, Monitoring, Databases, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-upwind-security-4460871956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lumana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-lumana-4463708633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist – MENTEE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mobileye</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Cloud (any), Terraform/IaC, Networking, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-%E2%80%93-mentee-at-mobileye-4445729205</t>
+    <t xml:space="preserve">Junior Power Control System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SolarEdge Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-power-control-system-engineer-at-solaredge-technologies-4438264844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operations Engineer II</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWeber</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uluberia-II,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-operations-engineer-ii-aweber-1136778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk &amp; Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tipuli Tech</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-support-specialist-at-tipuli-tech-4447121790</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Specialist for ROETO - Position No. 1717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IBI Investment House</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-for-roeto-position-no-1717-at-ibi-investment-house-4463025828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Working Student, Legal (German-speaking)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Via</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Berlin, Germany</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/via/jobs/8585955002</t>
   </si>
   <si>
     <t xml:space="preserve">2026-07-29</t>
   </si>
   <si>
-    <t xml:space="preserve">Junior Cloud Security Engineer (Entry-Level)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OnCloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cloud-security-engineer-entry-level-at-oncloud-4456904380</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TytoCare</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-tytocare-4461579939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator - 243425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experis Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-243425-at-experis-israel-4461821675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Operations &amp; Security Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PointFive</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Cloud (any), Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-security-specialist-at-pointfive-4426311043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Engineering INTERN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Cloud (any), CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineering-intern-at-microsoft-4451071541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raft Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4433796227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Enterprise Systems Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cross River</t>
-  </si>
-  <si>
-    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Azure, Cloud (any), Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-enterprise-systems-support-engineer-at-cross-river-4464614783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yael Korentec Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Virtualization, Active Directory, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-yael-korentec-technologies-4462122131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs JD Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days Open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Communication System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ceva, Inc.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/communication-system-engineer-at-ceva-inc-4459357209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fetcherr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-fetcherr-4449296509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Systems Engineer 2, Technical Operations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oracle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineer-2-technical-operations-at-oracle-4441078871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Center IT Technician - Masmiya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nebius</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-masmiya-at-nebius-4437672340</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Center IT Technician - Beit Shemesh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-beit-shemesh-at-nebius-4437673265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk &amp; Field Service Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stratasys</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-field-service-technician-at-stratasys-4461321939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer - Entry Level</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check Point Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-entry-level-at-check-point-software-4441459886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">איש/אשת תמיכה טכנית ו -Helpdesk 2+בפתח תקווה</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arad Tech - Technology, Engineering &amp; AI Recruitment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Networking, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%90%D7%99%D7%A9-%D7%90%D7%A9%D7%AA-%D7%AA%D7%9E%D7%99%D7%9B%D7%94-%D7%98%D7%9B%D7%A0%D7%99%D7%AA-%D7%95-helpdesk-2%2B%D7%91%D7%A4%D7%AA%D7%97-%D7%AA%D7%A7%D7%95%D7%95%D7%94-at-arad-tech-technology-engineering-ai-recruitment-4440622529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lab Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harmonic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/lab-support-engineer-at-harmonic-4448547160</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Service Desk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tata Consultancy Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/service-desk-specialist-at-tata-consultancy-services-4463224629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kaltura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-kaltura-4455279134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-tata-consultancy-services-4459788315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optimove</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estonia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-technician-at-comblack-4464328677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-kaltura-4460895402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COM-C-TECH LTD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory, Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-administrator-at-com-c-tech-ltd-4457234117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Platform Engineer - Student (Java)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-engineer-student-java-at-sap-4457493270</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Engineer- Student Position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Global-e</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-student-position-at-global-e-4455188600</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AudioCodes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-audiocodes-4454240269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Support Specialist (37425)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-support-specialist-37425-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4464324940</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-technician-at-abra-4454760617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Engineer (Tier 2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HCLTech</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-engineer-tier-2-at-hcltech-4445746731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tier I Technical Support Specialist — Smart Cooler Vending</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jobgether</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/tier-i-technical-support-specialist-%E2%80%94-smart-cooler-vending-at-jobgether-4463227567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Employer Branding Student (Temporary )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4912601101?gh_jid=4912601101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Power Control System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SolarEdge Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-power-control-system-engineer-at-solaredge-technologies-4438264844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk &amp; Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tipuli Tech</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-support-specialist-at-tipuli-tech-4447121790</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Desktop Support Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Impact Networks Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Be'er Sheva, South District, Israel</t>
+    <t xml:space="preserve">Student Success Coach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FindTutors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">London, London, England, United Kingdom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-student-success-coach-findtutors-1136086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roles requiring it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What to learn / where to start</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
   </si>
   <si>
     <t xml:space="preserve">Networking</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/desktop-support-technician-at-impact-networks-group-4464458660</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk (36409)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-36409-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4464346260</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Working Student, Legal (German-speaking)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Via</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Berlin, Germany</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/via/jobs/8585955002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roles requiring it</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What to learn / where to start</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
   </si>
   <si>
-    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
+    <t xml:space="preserve">Monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
   </si>
   <si>
     <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
   </si>
   <si>
-    <t xml:space="preserve">Monitoring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation</t>
-  </si>
-  <si>
     <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
   </si>
   <si>
+    <t xml:space="preserve">Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Bash/Shell</t>
   </si>
   <si>
     <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
   </si>
   <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
-  </si>
-  <si>
     <t xml:space="preserve">Python</t>
   </si>
   <si>
@@ -967,28 +841,25 @@
     <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
   </si>
   <si>
+    <t xml:space="preserve">Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free Docker Get Started tutorial + build 3 home-lab containers</t>
+  </si>
+  <si>
     <t xml:space="preserve">CI/CD</t>
   </si>
   <si>
     <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
   </si>
   <si>
-    <t xml:space="preserve">Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free Docker Get Started tutorial + build 3 home-lab containers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kubernetes.io tutorials → minikube on laptop → KCNA cert</t>
+    <t xml:space="preserve">Windows Server</t>
   </si>
   <si>
     <t xml:space="preserve">Count</t>
@@ -997,12 +868,12 @@
     <t xml:space="preserve">Pivot path advice</t>
   </si>
   <si>
+    <t xml:space="preserve">Already in IT — strengthen Linux + automation → apply to DevOps in 12-18mo.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tier 1/2 → SysAdmin → Junior DevOps. ~24 month path.</t>
   </si>
   <si>
-    <t xml:space="preserve">Already in IT — strengthen Linux + automation → apply to DevOps in 12-18mo.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cyclical — surge after bootcamp graduations (Aug/Feb).</t>
   </si>
   <si>
@@ -1025,9 +896,6 @@
   </si>
   <si>
     <t xml:space="preserve">yes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">remoteok</t>
   </si>
 </sst>
 </file>
@@ -1152,7 +1020,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>55</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7">
@@ -1160,7 +1028,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -1168,7 +1036,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9">
@@ -1176,7 +1044,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>517</v>
+        <v>511</v>
       </c>
     </row>
     <row r="10">
@@ -1258,7 +1126,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="22">
@@ -1266,7 +1134,7 @@
         <v>26</v>
       </c>
       <c r="B22" s="3">
-        <v>19</v>
+        <v>12</v>
       </c>
     </row>
     <row r="23">
@@ -1274,7 +1142,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24">
@@ -1316,7 +1184,7 @@
         <v>32</v>
       </c>
       <c r="B29" s="3">
-        <v>50</v>
+        <v>34</v>
       </c>
     </row>
     <row r="30">
@@ -1324,7 +1192,15 @@
         <v>33</v>
       </c>
       <c r="B30" s="3">
-        <v>5</v>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B31" s="3">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -1337,7 +1213,7 @@
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
     <col min="3" max="3" width="37" customWidth="1"/>
-    <col min="4" max="4" width="44" customWidth="1"/>
+    <col min="4" max="4" width="42" customWidth="1"/>
     <col min="5" max="5" width="31" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
     <col min="7" max="7" width="60" customWidth="1"/>
@@ -1348,34 +1224,34 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2">
@@ -1383,13 +1259,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>27</v>
@@ -1398,16 +1274,16 @@
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3">
@@ -1415,13 +1291,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>30</v>
@@ -1430,16 +1306,16 @@
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4">
@@ -1447,31 +1323,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F4" s="3">
         <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5">
@@ -1479,31 +1355,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F5" s="3">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="6">
@@ -1511,31 +1387,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F6" s="3">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7">
@@ -1543,31 +1419,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F7" s="3">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
     </row>
     <row r="8">
@@ -1575,31 +1451,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F8" s="3">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="9">
@@ -1607,31 +1483,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F9" s="3">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>33</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
     </row>
     <row r="10">
@@ -1639,31 +1515,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F10" s="3">
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="11">
@@ -1671,31 +1547,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>91</v>
+        <v>62</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F11" s="3">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>49</v>
+        <v>72</v>
       </c>
     </row>
     <row r="12">
@@ -1703,31 +1579,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F12" s="3">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="13">
@@ -1735,31 +1611,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>52</v>
+        <v>107</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F13" s="3">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
     </row>
     <row r="14">
@@ -1767,31 +1643,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F14" s="3">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
     </row>
     <row r="15">
@@ -1799,31 +1675,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>65</v>
+        <v>117</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F15" s="3">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>79</v>
+        <v>94</v>
       </c>
     </row>
     <row r="16">
@@ -1831,31 +1707,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>117</v>
+        <v>62</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F16" s="3">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="17">
@@ -1863,31 +1739,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F17" s="3">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>128</v>
+        <v>110</v>
       </c>
     </row>
     <row r="18">
@@ -1895,31 +1771,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>52</v>
+        <v>134</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F18" s="3">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>133</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19">
@@ -1927,31 +1803,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>134</v>
+        <v>62</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D19" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F19" s="3">
+        <v>32</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="J19" s="3" t="s">
         <v>72</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F19" s="3">
-        <v>46</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="20">
@@ -1959,31 +1835,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>65</v>
+        <v>141</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>140</v>
+        <v>53</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F20" s="3">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>143</v>
+        <v>50</v>
       </c>
     </row>
     <row r="21">
@@ -1991,19 +1867,19 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>146</v>
+        <v>47</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F21" s="3">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>147</v>
@@ -2015,7 +1891,7 @@
         <v>148</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>128</v>
+        <v>94</v>
       </c>
     </row>
     <row r="22">
@@ -2029,25 +1905,25 @@
         <v>150</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>67</v>
+        <v>151</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F22" s="3">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="23">
@@ -2055,31 +1931,31 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F23" s="3">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>49</v>
+        <v>72</v>
       </c>
     </row>
     <row r="24">
@@ -2087,19 +1963,19 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>159</v>
+        <v>141</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>160</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>52</v>
+        <v>113</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F24" s="3">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>161</v>
@@ -2125,25 +2001,25 @@
         <v>165</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>166</v>
+        <v>129</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F25" s="3">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="G25" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I25" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="H25" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I25" s="3" t="s">
+      <c r="J25" s="3" t="s">
         <v>168</v>
-      </c>
-      <c r="J25" s="3" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="26">
@@ -2151,31 +2027,31 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>65</v>
+        <v>169</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F26" s="3">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>79</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -2214,8 +2090,8 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="54" customWidth="1"/>
-    <col min="3" max="3" width="44" customWidth="1"/>
+    <col min="2" max="2" width="37" customWidth="1"/>
+    <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="31" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
@@ -2228,48 +2104,48 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>27</v>
@@ -2278,33 +2154,33 @@
         <v>100</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K2" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>30</v>
@@ -2313,640 +2189,640 @@
         <v>100</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K3" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E4" s="3">
         <v>100</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="K4" s="3">
-        <v>20</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E5" s="3">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="K5" s="3">
-        <v>89</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E6" s="3">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="K6" s="3">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E7" s="3">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="K7" s="3">
-        <v>1</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E8" s="3">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="K8" s="3">
-        <v>7</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E9" s="3">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>33</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="K9" s="3">
-        <v>44</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E10" s="3">
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="K10" s="3">
-        <v>22</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>91</v>
+        <v>62</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E11" s="3">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="K11" s="3">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E12" s="3">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="K12" s="3">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>52</v>
+        <v>107</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E13" s="3">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="K13" s="3">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E14" s="3">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="K14" s="3">
-        <v>69</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>65</v>
+        <v>117</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E15" s="3">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="K15" s="3">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>117</v>
+        <v>62</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E16" s="3">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="K16" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E17" s="3">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>128</v>
+        <v>110</v>
       </c>
       <c r="K17" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>52</v>
+        <v>134</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E18" s="3">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>133</v>
+        <v>50</v>
       </c>
       <c r="K18" s="3">
-        <v>42</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>134</v>
+        <v>62</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C19" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E19" s="3">
+        <v>32</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="J19" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="D19" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E19" s="3">
-        <v>46</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>138</v>
-      </c>
       <c r="K19" s="3">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>65</v>
+        <v>141</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>140</v>
+        <v>53</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E20" s="3">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>143</v>
+        <v>50</v>
       </c>
       <c r="K20" s="3">
-        <v>8</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>146</v>
+        <v>47</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E21" s="3">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>147</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>32</v>
@@ -2955,10 +2831,10 @@
         <v>148</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>128</v>
+        <v>94</v>
       </c>
       <c r="K21" s="3">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22">
@@ -2969,89 +2845,89 @@
         <v>150</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>67</v>
+        <v>151</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E22" s="3">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="K22" s="3">
-        <v>26</v>
+        <v>14</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E23" s="3">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="K23" s="3">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>159</v>
+        <v>141</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>160</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>52</v>
+        <v>113</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E24" s="3">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>161</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>32</v>
@@ -3063,7 +2939,7 @@
         <v>163</v>
       </c>
       <c r="K24" s="3">
-        <v>58</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25">
@@ -3074,474 +2950,474 @@
         <v>165</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>166</v>
+        <v>129</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E25" s="3">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="F25" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I25" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="G25" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I25" s="3" t="s">
+      <c r="J25" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="J25" s="3" t="s">
-        <v>55</v>
-      </c>
       <c r="K25" s="3">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>65</v>
+        <v>169</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E26" s="3">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>79</v>
+        <v>56</v>
       </c>
       <c r="K26" s="3">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>46</v>
+        <v>113</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E27" s="3">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>106</v>
+        <v>56</v>
       </c>
       <c r="K27" s="3">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>140</v>
+        <v>186</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E28" s="3">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H28" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="K28" s="3">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>159</v>
+        <v>189</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>72</v>
+        <v>134</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E29" s="3">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>190</v>
+        <v>168</v>
       </c>
       <c r="K29" s="3">
-        <v>21</v>
+        <v>27</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>146</v>
+        <v>195</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E30" s="3">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="K30" s="3">
-        <v>24</v>
+        <v>17</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>156</v>
+        <v>101</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E31" s="3">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>200</v>
+        <v>94</v>
       </c>
       <c r="K31" s="3">
-        <v>54</v>
+        <v>10</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E32" s="3">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>153</v>
+        <v>116</v>
       </c>
       <c r="K32" s="3">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>204</v>
+        <v>46</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>205</v>
+        <v>47</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E33" s="3">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>55</v>
+        <v>116</v>
       </c>
       <c r="K33" s="3">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>52</v>
+        <v>123</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E34" s="3">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H34" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>153</v>
+        <v>213</v>
       </c>
       <c r="K34" s="3">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>146</v>
+        <v>216</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E35" s="3">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="K35" s="3">
-        <v>55</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>217</v>
+        <v>199</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>125</v>
+        <v>220</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E36" s="3">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H36" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>221</v>
+        <v>83</v>
       </c>
       <c r="K36" s="3">
-        <v>34</v>
+        <v>23</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>223</v>
+        <v>74</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E37" s="3">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F37" s="3" t="s">
         <v>224</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I37" s="3" t="s">
         <v>225</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>55</v>
+        <v>226</v>
       </c>
       <c r="K37" s="3">
-        <v>0</v>
+        <v>70</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>228</v>
+        <v>157</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E38" s="3">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="F38" s="3" t="s">
         <v>229</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H38" s="3" t="s">
         <v>32</v>
@@ -3550,642 +3426,185 @@
         <v>230</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>190</v>
+        <v>83</v>
       </c>
       <c r="K38" s="3">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>159</v>
+        <v>231</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>146</v>
+        <v>233</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E39" s="3">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>143</v>
+        <v>213</v>
       </c>
       <c r="K39" s="3">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E40" s="3">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="K40" s="3">
-        <v>16</v>
+        <v>39</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>71</v>
+        <v>242</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E41" s="3">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>241</v>
+        <v>213</v>
       </c>
       <c r="K41" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>227</v>
+        <v>245</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>119</v>
+        <v>246</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E42" s="3">
-        <v>10</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>243</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F42" s="3"/>
       <c r="G42" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>106</v>
+        <v>248</v>
       </c>
       <c r="K42" s="3">
-        <v>9</v>
+        <v>43</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E43" s="3">
-        <v>9</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>248</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F43" s="3"/>
       <c r="G43" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>138</v>
+        <v>253</v>
       </c>
       <c r="K43" s="3">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E44" s="3">
-        <v>8</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="G44" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H44" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I44" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="J44" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="K44" s="3">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E45" s="3">
-        <v>8</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="J45" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="K45" s="3">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>259</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E46" s="3">
-        <v>6</v>
-      </c>
-      <c r="F46" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="G46" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H46" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I46" s="3" t="s">
-        <v>261</v>
-      </c>
-      <c r="J46" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="K46" s="3">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="D47" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E47" s="3">
-        <v>6</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="K47" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="D48" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E48" s="3">
-        <v>6</v>
-      </c>
-      <c r="F48" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="G48" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H48" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I48" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="J48" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="K48" s="3">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="D49" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E49" s="3">
-        <v>6</v>
-      </c>
-      <c r="F49" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="G49" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H49" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="K49" s="3">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="D50" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E50" s="3">
-        <v>6</v>
-      </c>
-      <c r="F50" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="G50" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H50" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I50" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="J50" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="K50" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="3" t="s">
-        <v>273</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="D51" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E51" s="3">
-        <v>4</v>
-      </c>
-      <c r="F51" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="G51" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H51" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I51" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="J51" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="K51" s="3">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="3" t="s">
-        <v>276</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="D52" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E52" s="3">
-        <v>4</v>
-      </c>
-      <c r="F52" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="G52" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H52" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="J52" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="K52" s="3">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="3" t="s">
-        <v>280</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>281</v>
-      </c>
-      <c r="C53" s="3" t="s">
-        <v>282</v>
-      </c>
-      <c r="D53" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E53" s="3">
-        <v>3</v>
-      </c>
-      <c r="F53" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="G53" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H53" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I53" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="J53" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="K53" s="3">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="C54" s="3" t="s">
-        <v>287</v>
-      </c>
-      <c r="D54" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E54" s="3">
-        <v>3</v>
-      </c>
-      <c r="F54" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="G54" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H54" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I54" s="3" t="s">
-        <v>289</v>
-      </c>
-      <c r="J54" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="K54" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="3" t="s">
-        <v>290</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="C55" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="D55" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E55" s="3">
-        <v>3</v>
-      </c>
-      <c r="F55" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="G55" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H55" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I55" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="J55" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="K55" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="3" t="s">
-        <v>292</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="C56" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="D56" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E56" s="3">
-        <v>0</v>
-      </c>
-      <c r="F56" s="3"/>
-      <c r="G56" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H56" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I56" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="J56" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="K56" s="3">
-        <v>42</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K56"/>
+  <autoFilter ref="A1:K43"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1"/>
     <hyperlink ref="I3" r:id="rId2"/>
@@ -4229,19 +3648,6 @@
     <hyperlink ref="I41" r:id="rId40"/>
     <hyperlink ref="I42" r:id="rId41"/>
     <hyperlink ref="I43" r:id="rId42"/>
-    <hyperlink ref="I44" r:id="rId43"/>
-    <hyperlink ref="I45" r:id="rId44"/>
-    <hyperlink ref="I46" r:id="rId45"/>
-    <hyperlink ref="I47" r:id="rId46"/>
-    <hyperlink ref="I48" r:id="rId47"/>
-    <hyperlink ref="I49" r:id="rId48"/>
-    <hyperlink ref="I50" r:id="rId49"/>
-    <hyperlink ref="I51" r:id="rId50"/>
-    <hyperlink ref="I52" r:id="rId51"/>
-    <hyperlink ref="I53" r:id="rId52"/>
-    <hyperlink ref="I54" r:id="rId53"/>
-    <hyperlink ref="I55" r:id="rId54"/>
-    <hyperlink ref="I56" r:id="rId55"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -4250,232 +3656,136 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="24" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="60" customWidth="1"/>
+    <col min="5" max="5" width="29" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>50</v>
+        <v>209</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>51</v>
+        <v>210</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D2" s="3">
-        <v>100</v>
+        <v>8</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>53</v>
+        <v>211</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>54</v>
+        <v>212</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>55</v>
+        <v>213</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>164</v>
+        <v>214</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>165</v>
+        <v>215</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D3" s="3">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>167</v>
+        <v>217</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>168</v>
+        <v>218</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>55</v>
+        <v>213</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>203</v>
+        <v>231</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>204</v>
+        <v>232</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D4" s="3">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>206</v>
+        <v>234</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>207</v>
+        <v>235</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>55</v>
+        <v>213</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>222</v>
+        <v>241</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>223</v>
+        <v>242</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D5" s="3">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>225</v>
+        <v>243</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D6" s="3">
-        <v>6</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D7" s="3">
-        <v>6</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D8" s="3">
-        <v>3</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>289</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="s">
-        <v>290</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D9" s="3">
-        <v>3</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>55</v>
+        <v>213</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G9"/>
+  <autoFilter ref="A1:G5"/>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1"/>
     <hyperlink ref="F3" r:id="rId2"/>
     <hyperlink ref="F4" r:id="rId3"/>
     <hyperlink ref="F5" r:id="rId4"/>
-    <hyperlink ref="F6" r:id="rId5"/>
-    <hyperlink ref="F7" r:id="rId6"/>
-    <hyperlink ref="F8" r:id="rId7"/>
-    <hyperlink ref="F9" r:id="rId8"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -4490,178 +3800,178 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>296</v>
+        <v>254</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>297</v>
+        <v>255</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>298</v>
+        <v>256</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>278</v>
+        <v>229</v>
       </c>
       <c r="B2" s="3">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>299</v>
+        <v>257</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>288</v>
+        <v>224</v>
       </c>
       <c r="B3" s="3">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>300</v>
+        <v>258</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>274</v>
+        <v>259</v>
       </c>
       <c r="B4" s="3">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>301</v>
+        <v>260</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>239</v>
+        <v>261</v>
       </c>
       <c r="B5" s="3">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>302</v>
+        <v>262</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>303</v>
+        <v>191</v>
       </c>
       <c r="B6" s="3">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>304</v>
+        <v>263</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>305</v>
+        <v>234</v>
       </c>
       <c r="B7" s="3">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>306</v>
+        <v>264</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>307</v>
+        <v>265</v>
       </c>
       <c r="B8" s="3">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>308</v>
+        <v>266</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>309</v>
+        <v>267</v>
       </c>
       <c r="B9" s="3">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>310</v>
+        <v>268</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>311</v>
+        <v>269</v>
       </c>
       <c r="B10" s="3">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>312</v>
+        <v>270</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>313</v>
+        <v>271</v>
       </c>
       <c r="B11" s="3">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>314</v>
+        <v>272</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>315</v>
+        <v>273</v>
       </c>
       <c r="B12" s="3">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>316</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>317</v>
+        <v>275</v>
       </c>
       <c r="B13" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>318</v>
+        <v>276</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>319</v>
+        <v>277</v>
       </c>
       <c r="B14" s="3">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>320</v>
+        <v>278</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>321</v>
+        <v>279</v>
       </c>
       <c r="B15" s="3">
         <v>7</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>322</v>
+        <v>280</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>323</v>
+        <v>281</v>
       </c>
       <c r="B16" s="3">
         <v>7</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>324</v>
+        <v>276</v>
       </c>
     </row>
   </sheetData>
@@ -4678,13 +3988,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>325</v>
+        <v>282</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>326</v>
+        <v>283</v>
       </c>
     </row>
     <row r="2">
@@ -4692,10 +4002,10 @@
         <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>327</v>
+        <v>284</v>
       </c>
     </row>
     <row r="3">
@@ -4703,10 +4013,10 @@
         <v>26</v>
       </c>
       <c r="B3" s="3">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>328</v>
+        <v>285</v>
       </c>
     </row>
     <row r="4">
@@ -4714,10 +4024,10 @@
         <v>27</v>
       </c>
       <c r="B4" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>329</v>
+        <v>286</v>
       </c>
     </row>
     <row r="5">
@@ -4728,7 +4038,7 @@
         <v>2</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>330</v>
+        <v>287</v>
       </c>
     </row>
     <row r="6">
@@ -4739,7 +4049,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>331</v>
+        <v>288</v>
       </c>
     </row>
     <row r="7">
@@ -4750,7 +4060,7 @@
         <v>1</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>332</v>
+        <v>289</v>
       </c>
     </row>
   </sheetData>
@@ -4768,16 +4078,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>333</v>
+        <v>290</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>334</v>
+        <v>291</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>335</v>
+        <v>292</v>
       </c>
     </row>
     <row r="2">
@@ -4785,10 +4095,10 @@
         <v>33</v>
       </c>
       <c r="B2" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>336</v>
+        <v>293</v>
       </c>
       <c r="D2" s="3"/>
     </row>
@@ -4797,22 +4107,22 @@
         <v>32</v>
       </c>
       <c r="B3" s="3">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>336</v>
+        <v>293</v>
       </c>
       <c r="D3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>337</v>
+        <v>34</v>
       </c>
       <c r="B4" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>336</v>
+        <v>293</v>
       </c>
       <c r="D4" s="3"/>
     </row>

--- a/reports/devops-juniors-israel-2026-W37.xlsx
+++ b/reports/devops-juniors-israel-2026-W37.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="294">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="262">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10T11:10:19</t>
+    <t xml:space="preserve">2026-09-11T11:09:59</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -94,21 +94,21 @@
     <t xml:space="preserve">SysAdmin / NOC</t>
   </si>
   <si>
+    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
+  </si>
+  <si>
     <t xml:space="preserve">Help Desk / IT Support</t>
   </si>
   <si>
-    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
-  </si>
-  <si>
     <t xml:space="preserve">Junior SysAdmin / Linux</t>
   </si>
   <si>
+    <t xml:space="preserve">Junior DevOps</t>
+  </si>
+  <si>
     <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
   </si>
   <si>
-    <t xml:space="preserve">Junior DevOps</t>
-  </si>
-  <si>
     <t xml:space="preserve">By source</t>
   </si>
   <si>
@@ -187,355 +187,352 @@
     <t xml:space="preserve">2026-09-09</t>
   </si>
   <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-12</t>
+    <t xml:space="preserve">NOC Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rapyd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-team-leader-at-rapyd-4428470164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel - Raanana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4850412101?gh_jid=4850412101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Technical Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iGATES - INFORMATION GATES Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-operations-engineer-at-igates-information-gates-ltd-4452212223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Intern</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CertifyOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pune</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, GCP, Cloud (any), Kubernetes, CI/CD, Git, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-ai-intern-certifyos-1135555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Engineer Student, SPIV team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amazon Web Services (AWS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, CI/CD, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-student-spiv-team-at-amazon-web-services-aws-4456348779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Production Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Torq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6179167004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer (NOC / Tier 1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kela Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-noc-tier-1-at-kela-technologies-4461059776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upwind Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Networking, Monitoring, Databases, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-upwind-security-4460871956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lumana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-lumana-4463708633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Cloud Security Engineer (Entry-Level)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OnCloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cloud-security-engineer-entry-level-at-oncloud-4456904380</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-26</t>
   </si>
   <si>
     <t xml:space="preserve">System Administrator</t>
   </si>
   <si>
+    <t xml:space="preserve">TytoCare</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-tytocare-4461579939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator - 243425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experis Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-243425-at-experis-israel-4461821675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Engineering INTERN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Cloud (any), CI/CD, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineering-intern-at-microsoft-4451071541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raft Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4433796227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gini-Apps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Networking, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-gini-apps-4440026223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Communication System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ceva, Inc.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/communication-system-engineer-at-ceva-inc-4459357209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fetcherr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, CI/CD, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-fetcherr-4449296509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Field Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mornex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-field-support-engineer-at-mornex-4457946363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator (24/7 Shift-Based)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">evoke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-24-7-shift-based-at-evoke-4462157700</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring Technical Support Specialist (NOC)</t>
+  </si>
+  <si>
     <t xml:space="preserve">SuperCom (NASDAQ: SPCB)</t>
   </si>
   <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, Cloud (any), CI/CD, Git, Networking, Monitoring, Databases, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-supercom-nasdaq-spcb-4462293466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator (Nutanix Expert)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">peax dorcom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, AWS, Azure, GCP, Cloud (any), Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-nutanix-expert-at-peax-dorcom-4459918624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel - Raanana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4850412101?gh_jid=4850412101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Technical Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iGATES - INFORMATION GATES Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-operations-engineer-at-igates-information-gates-ltd-4452212223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Production Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Torq</t>
-  </si>
-  <si>
-    <t xml:space="preserve">israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6179167004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer (NOC / Tier 1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kela Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-noc-tier-1-at-kela-technologies-4461059776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CONTROP Precision Technologies Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Networking, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-controp-precision-technologies-ltd-4460943847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upwind Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Networking, Monitoring, Databases, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-upwind-security-4460871956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lumana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-lumana-4463708633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Cloud Security Engineer (Entry-Level)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OnCloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cloud-security-engineer-entry-level-at-oncloud-4456904380</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Operations Analyst Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Forter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel - Tel Aviv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/forter/jobs/8759588002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TytoCare</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-tytocare-4461579939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator - 243425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experis Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-243425-at-experis-israel-4461821675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Engineering INTERN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Cloud (any), CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineering-intern-at-microsoft-4451071541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yael Korentec Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Virtualization, Active Directory, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-yael-korentec-technologies-4462122131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gini-Apps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Networking, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-gini-apps-4440026223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Communication System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ceva, Inc.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/communication-system-engineer-at-ceva-inc-4459357209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Field Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mornex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-field-support-engineer-at-mornex-4457946363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator (24/7 Shift-Based)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">evoke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-24-7-shift-based-at-evoke-4462157700</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Systems Engineer 2, Technical Operations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oracle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineer-2-technical-operations-at-oracle-4444274357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk &amp; Field Service Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stratasys</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-field-service-technician-at-stratasys-4461321939</t>
+    <t xml:space="preserve">AWS, Cloud (any), Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/monitoring-technical-support-specialist-noc-at-supercom-nasdaq-spcb-4465838312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tata Consultancy Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-tata-consultancy-services-4459788315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WaveBL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc%0A%09%09%09%09%09%09%09%09%09%0A%09%09%09%09%09%09%09%09%0A%09%09%09%09%09%09%09%09%09%09israel-at-wavebl-4443917908</t>
   </si>
   <si>
     <t xml:space="preserve">Title</t>
@@ -556,45 +553,6 @@
     <t xml:space="preserve">no</t>
   </si>
   <si>
-    <t xml:space="preserve">Service Desk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tata Consultancy Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/service-desk-specialist-at-tata-consultancy-services-4463224629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kaltura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-kaltura-4455279134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WaveBL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc%0A%09%09%09%09%09%09%09%09%09%0A%09%09%09%09%09%09%09%09%0A%09%09%09%09%09%09%09%09%09%09israel-at-wavebl-4443917908</t>
-  </si>
-  <si>
     <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
   </si>
   <si>
@@ -604,24 +562,12 @@
     <t xml:space="preserve">Estonia</t>
   </si>
   <si>
-    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
   </si>
   <si>
     <t xml:space="preserve">2026-08-24</t>
   </si>
   <si>
-    <t xml:space="preserve">Help Desk Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-kaltura-4460895402</t>
-  </si>
-  <si>
     <t xml:space="preserve">Junior System Administrator</t>
   </si>
   <si>
@@ -658,31 +604,13 @@
     <t xml:space="preserve">2026-09-10</t>
   </si>
   <si>
-    <t xml:space="preserve">System administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NBS-HR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shoham, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-nbs-hr-4463014591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AudioCodes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-audiocodes-4454240269</t>
+    <t xml:space="preserve">NOC Engineer- Student Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Global-e</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-student-position-at-global-e-4463461048</t>
   </si>
   <si>
     <t xml:space="preserve">Employer Branding Student (Temporary )</t>
@@ -724,30 +652,6 @@
     <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-operations-engineer-ii-aweber-1136778</t>
   </si>
   <si>
-    <t xml:space="preserve">Help Desk &amp; Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tipuli Tech</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-support-specialist-at-tipuli-tech-4447121790</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Specialist for ROETO - Position No. 1717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IBI Investment House</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-for-roeto-position-no-1717-at-ibi-investment-house-4463025828</t>
-  </si>
-  <si>
     <t xml:space="preserve">Working Student, Legal (German-speaking)</t>
   </si>
   <si>
@@ -760,9 +664,6 @@
     <t xml:space="preserve">https://job-boards.greenhouse.io/via/jobs/8585955002</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-29</t>
-  </si>
-  <si>
     <t xml:space="preserve">Student Success Coach</t>
   </si>
   <si>
@@ -790,31 +691,43 @@
     <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
   </si>
   <si>
+    <t xml:space="preserve">Monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
+  </si>
+  <si>
     <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
   </si>
   <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
+  </si>
+  <si>
     <t xml:space="preserve">Networking</t>
   </si>
   <si>
     <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
   </si>
   <si>
-    <t xml:space="preserve">Monitoring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
   </si>
   <si>
     <t xml:space="preserve">Azure</t>
@@ -829,22 +742,10 @@
     <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
   </si>
   <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kubernetes.io tutorials → minikube on laptop → KCNA cert</t>
   </si>
   <si>
     <t xml:space="preserve">Docker</t>
@@ -853,13 +754,16 @@
     <t xml:space="preserve">Free Docker Get Started tutorial + build 3 home-lab containers</t>
   </si>
   <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Windows Server</t>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google Cloud Skills Boost (free) → ACE cert</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Git</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pro Git book (free online) + create a learning repo</t>
   </si>
   <si>
     <t xml:space="preserve">Count</t>
@@ -871,19 +775,19 @@
     <t xml:space="preserve">Already in IT — strengthen Linux + automation → apply to DevOps in 12-18mo.</t>
   </si>
   <si>
+    <t xml:space="preserve">Cyclical — surge after bootcamp graduations (Aug/Feb).</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tier 1/2 → SysAdmin → Junior DevOps. ~24 month path.</t>
   </si>
   <si>
-    <t xml:space="preserve">Cyclical — surge after bootcamp graduations (Aug/Feb).</t>
-  </si>
-  <si>
     <t xml:space="preserve">12-18 months → Junior DevOps. Strengthen Linux + Python + AWS.</t>
   </si>
   <si>
+    <t xml:space="preserve">Direct DevOps role — apply aggressively. Rare and competitive.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Often paired with on-call. Strong learning track.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Direct DevOps role — apply aggressively. Rare and competitive.</t>
   </si>
   <si>
     <t xml:space="preserve">Jobs</t>
@@ -1020,7 +924,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>42</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7">
@@ -1028,7 +932,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -1036,7 +940,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -1044,7 +948,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="10">
@@ -1126,7 +1030,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22">
@@ -1134,7 +1038,7 @@
         <v>26</v>
       </c>
       <c r="B22" s="3">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23">
@@ -1142,7 +1046,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24">
@@ -1184,7 +1088,7 @@
         <v>32</v>
       </c>
       <c r="B29" s="3">
-        <v>34</v>
+        <v>27</v>
       </c>
     </row>
     <row r="30">
@@ -1192,7 +1096,7 @@
         <v>33</v>
       </c>
       <c r="B30" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31">
@@ -1200,7 +1104,7 @@
         <v>34</v>
       </c>
       <c r="B31" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -1212,7 +1116,7 @@
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
-    <col min="3" max="3" width="37" customWidth="1"/>
+    <col min="3" max="3" width="32" customWidth="1"/>
     <col min="4" max="4" width="42" customWidth="1"/>
     <col min="5" max="5" width="31" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
@@ -1268,7 +1172,7 @@
         <v>47</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
@@ -1300,7 +1204,7 @@
         <v>53</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
@@ -1347,7 +1251,7 @@
         <v>60</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5">
@@ -1355,31 +1259,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="D5" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="E5" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" s="3">
+        <v>83</v>
+      </c>
+      <c r="G5" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F5" s="3">
-        <v>96</v>
-      </c>
-      <c r="G5" s="3" t="s">
+      <c r="H5" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I5" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="H5" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I5" s="3" t="s">
+      <c r="J5" s="3" t="s">
         <v>66</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="6">
@@ -1387,31 +1291,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>69</v>
-      </c>
       <c r="D6" s="3" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F6" s="3">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="G6" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I6" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="H6" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I6" s="3" t="s">
+      <c r="J6" s="3" t="s">
         <v>71</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="7">
@@ -1419,31 +1323,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="D7" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="E7" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" s="3">
+        <v>79</v>
+      </c>
+      <c r="G7" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="E7" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F7" s="3">
-        <v>83</v>
-      </c>
-      <c r="G7" s="3" t="s">
+      <c r="H7" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I7" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="H7" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I7" s="3" t="s">
+      <c r="J7" s="3" t="s">
         <v>77</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="8">
@@ -1451,19 +1355,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="D8" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>53</v>
-      </c>
       <c r="E8" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F8" s="3">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>81</v>
@@ -1475,7 +1379,7 @@
         <v>82</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>83</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9">
@@ -1483,13 +1387,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="D9" s="3" t="s">
         <v>85</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>86</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>25</v>
@@ -1498,16 +1402,16 @@
         <v>68</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>33</v>
       </c>
       <c r="I9" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="J9" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="10">
@@ -1515,31 +1419,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>90</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>53</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F10" s="3">
         <v>61</v>
       </c>
       <c r="G10" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I10" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="H10" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I10" s="3" t="s">
+      <c r="J10" s="3" t="s">
         <v>93</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="11">
@@ -1547,7 +1451,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>95</v>
@@ -1556,10 +1460,10 @@
         <v>96</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F11" s="3">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>97</v>
@@ -1571,7 +1475,7 @@
         <v>98</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>72</v>
+        <v>99</v>
       </c>
     </row>
     <row r="12">
@@ -1579,31 +1483,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F12" s="3">
         <v>47</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="13">
@@ -1611,31 +1515,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F13" s="3">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="14">
@@ -1643,31 +1547,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F14" s="3">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="15">
@@ -1675,31 +1579,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F15" s="3">
         <v>44</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
     </row>
     <row r="16">
@@ -1707,31 +1611,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>62</v>
+        <v>123</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F16" s="3">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>126</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17">
@@ -1739,19 +1643,19 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>129</v>
+        <v>53</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F17" s="3">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>130</v>
@@ -1763,7 +1667,7 @@
         <v>131</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>110</v>
+        <v>132</v>
       </c>
     </row>
     <row r="18">
@@ -1771,28 +1675,28 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>133</v>
       </c>
       <c r="D18" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F18" s="3">
+        <v>28</v>
+      </c>
+      <c r="G18" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="E18" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F18" s="3">
-        <v>39</v>
-      </c>
-      <c r="G18" s="3" t="s">
+      <c r="H18" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I18" s="3" t="s">
         <v>135</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>136</v>
       </c>
       <c r="J18" s="3" t="s">
         <v>50</v>
@@ -1803,31 +1707,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>62</v>
+        <v>136</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>137</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>138</v>
+        <v>47</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F19" s="3">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="G19" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I19" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="H19" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>140</v>
-      </c>
       <c r="J19" s="3" t="s">
-        <v>72</v>
+        <v>93</v>
       </c>
     </row>
     <row r="20">
@@ -1835,31 +1739,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="D20" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F20" s="3">
+        <v>27</v>
+      </c>
+      <c r="G20" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F20" s="3">
-        <v>28</v>
-      </c>
-      <c r="G20" s="3" t="s">
+      <c r="H20" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I20" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I20" s="3" t="s">
+      <c r="J20" s="3" t="s">
         <v>144</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="21">
@@ -1873,25 +1777,25 @@
         <v>146</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>47</v>
+        <v>147</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F21" s="3">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>94</v>
+        <v>150</v>
       </c>
     </row>
     <row r="22">
@@ -1899,31 +1803,31 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F22" s="3">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="23">
@@ -1931,13 +1835,13 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>155</v>
+        <v>128</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>157</v>
+        <v>108</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>25</v>
@@ -1955,7 +1859,7 @@
         <v>159</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>72</v>
+        <v>160</v>
       </c>
     </row>
     <row r="24">
@@ -1963,31 +1867,31 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>141</v>
+        <v>161</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>113</v>
+        <v>53</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F24" s="3">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="25">
@@ -1995,31 +1899,31 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>164</v>
+        <v>128</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F25" s="3">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>168</v>
+        <v>117</v>
       </c>
     </row>
     <row r="26">
@@ -2033,25 +1937,25 @@
         <v>170</v>
       </c>
       <c r="D26" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F26" s="3">
+        <v>12</v>
+      </c>
+      <c r="G26" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="E26" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F26" s="3">
-        <v>20</v>
-      </c>
-      <c r="G26" s="3" t="s">
+      <c r="H26" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I26" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="H26" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>173</v>
-      </c>
       <c r="J26" s="3" t="s">
-        <v>56</v>
+        <v>144</v>
       </c>
     </row>
   </sheetData>
@@ -2090,7 +1994,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="37" customWidth="1"/>
+    <col min="2" max="2" width="32" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="31" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
@@ -2104,7 +2008,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>37</v>
@@ -2119,22 +2023,22 @@
         <v>40</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>175</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>176</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>42</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>44</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="2">
@@ -2148,7 +2052,7 @@
         <v>47</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E2" s="3">
         <v>100</v>
@@ -2157,7 +2061,7 @@
         <v>48</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>32</v>
@@ -2169,7 +2073,7 @@
         <v>50</v>
       </c>
       <c r="K2" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3">
@@ -2183,7 +2087,7 @@
         <v>53</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E3" s="3">
         <v>100</v>
@@ -2192,7 +2096,7 @@
         <v>54</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>32</v>
@@ -2204,7 +2108,7 @@
         <v>56</v>
       </c>
       <c r="K3" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -2227,7 +2131,7 @@
         <v>59</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>32</v>
@@ -2236,138 +2140,138 @@
         <v>60</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="K4" s="3">
-        <v>90</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="C5" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="D5" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" s="3">
+        <v>83</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E5" s="3">
-        <v>96</v>
-      </c>
-      <c r="F5" s="3" t="s">
+      <c r="G5" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I5" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="G5" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I5" s="3" t="s">
+      <c r="J5" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="J5" s="3" t="s">
-        <v>67</v>
-      </c>
       <c r="K5" s="3">
-        <v>2</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>69</v>
-      </c>
       <c r="C6" s="3" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E6" s="3">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F6" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I6" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="G6" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I6" s="3" t="s">
+      <c r="J6" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="J6" s="3" t="s">
-        <v>72</v>
-      </c>
       <c r="K6" s="3">
-        <v>8</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="C7" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="D7" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" s="3">
+        <v>79</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E7" s="3">
-        <v>83</v>
-      </c>
-      <c r="F7" s="3" t="s">
+      <c r="G7" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I7" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="G7" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I7" s="3" t="s">
+      <c r="J7" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="J7" s="3" t="s">
-        <v>78</v>
-      </c>
       <c r="K7" s="3">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="C8" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>53</v>
-      </c>
       <c r="D8" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E8" s="3">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>81</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>32</v>
@@ -2376,21 +2280,21 @@
         <v>82</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>83</v>
+        <v>50</v>
       </c>
       <c r="K8" s="3">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="C9" s="3" t="s">
         <v>85</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>86</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>25</v>
@@ -2399,62 +2303,62 @@
         <v>68</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>33</v>
       </c>
       <c r="I9" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="J9" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="J9" s="3" t="s">
-        <v>89</v>
-      </c>
       <c r="K9" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>90</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>53</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E10" s="3">
         <v>61</v>
       </c>
       <c r="F10" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I10" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="G10" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I10" s="3" t="s">
+      <c r="J10" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="J10" s="3" t="s">
-        <v>94</v>
-      </c>
       <c r="K10" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>95</v>
@@ -2463,16 +2367,16 @@
         <v>96</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E11" s="3">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F11" s="3" t="s">
         <v>97</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>32</v>
@@ -2481,208 +2385,208 @@
         <v>98</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>72</v>
+        <v>99</v>
       </c>
       <c r="K11" s="3">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E12" s="3">
         <v>47</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K12" s="3">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E13" s="3">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K13" s="3">
-        <v>4</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E14" s="3">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K14" s="3">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E15" s="3">
         <v>44</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="K15" s="3">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>62</v>
+        <v>123</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E16" s="3">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>126</v>
+        <v>50</v>
       </c>
       <c r="K16" s="3">
-        <v>9</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>129</v>
+        <v>53</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E17" s="3">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>130</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>32</v>
@@ -2691,115 +2595,115 @@
         <v>131</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>110</v>
+        <v>132</v>
       </c>
       <c r="K17" s="3">
-        <v>4</v>
+        <v>60</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>133</v>
       </c>
       <c r="C18" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E18" s="3">
+        <v>28</v>
+      </c>
+      <c r="F18" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E18" s="3">
-        <v>39</v>
-      </c>
-      <c r="F18" s="3" t="s">
+      <c r="G18" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I18" s="3" t="s">
         <v>135</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>136</v>
       </c>
       <c r="J18" s="3" t="s">
         <v>50</v>
       </c>
       <c r="K18" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>62</v>
+        <v>136</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>137</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>138</v>
+        <v>47</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E19" s="3">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F19" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I19" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="G19" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>140</v>
-      </c>
       <c r="J19" s="3" t="s">
-        <v>72</v>
+        <v>93</v>
       </c>
       <c r="K19" s="3">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="B20" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="C20" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E20" s="3">
+        <v>27</v>
+      </c>
+      <c r="F20" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="C20" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="K20" s="3">
         <v>28</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="K20" s="3">
-        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -2810,77 +2714,77 @@
         <v>146</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>47</v>
+        <v>147</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E21" s="3">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>94</v>
+        <v>150</v>
       </c>
       <c r="K21" s="3">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E22" s="3">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="K22" s="3">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>155</v>
+        <v>128</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>157</v>
+        <v>108</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>25</v>
@@ -2892,7 +2796,7 @@
         <v>158</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>32</v>
@@ -2901,80 +2805,80 @@
         <v>159</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>72</v>
+        <v>160</v>
       </c>
       <c r="K23" s="3">
-        <v>8</v>
+        <v>23</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>141</v>
+        <v>161</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>113</v>
+        <v>53</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E24" s="3">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="K24" s="3">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>164</v>
+        <v>128</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E25" s="3">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>168</v>
+        <v>117</v>
       </c>
       <c r="K25" s="3">
-        <v>27</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26">
@@ -2985,66 +2889,66 @@
         <v>170</v>
       </c>
       <c r="C26" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E26" s="3">
+        <v>12</v>
+      </c>
+      <c r="F26" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E26" s="3">
-        <v>20</v>
-      </c>
-      <c r="F26" s="3" t="s">
+      <c r="G26" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I26" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="G26" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>173</v>
-      </c>
       <c r="J26" s="3" t="s">
-        <v>56</v>
+        <v>144</v>
       </c>
       <c r="K26" s="3">
-        <v>1</v>
+        <v>28</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="B27" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="C27" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="C27" s="3" t="s">
-        <v>113</v>
-      </c>
       <c r="D27" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E27" s="3">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F27" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I27" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="G27" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I27" s="3" t="s">
+      <c r="J27" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="J27" s="3" t="s">
-        <v>56</v>
-      </c>
       <c r="K27" s="3">
-        <v>1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="28">
@@ -3055,556 +2959,311 @@
         <v>185</v>
       </c>
       <c r="C28" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E28" s="3">
+        <v>9</v>
+      </c>
+      <c r="F28" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="D28" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E28" s="3">
-        <v>13</v>
-      </c>
-      <c r="F28" s="3" t="s">
+      <c r="G28" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I28" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="G28" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="H28" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I28" s="3" t="s">
-        <v>188</v>
-      </c>
       <c r="J28" s="3" t="s">
-        <v>163</v>
+        <v>111</v>
       </c>
       <c r="K28" s="3">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E29" s="3">
+        <v>8</v>
+      </c>
+      <c r="F29" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="G29" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I29" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="C29" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E29" s="3">
-        <v>12</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>192</v>
-      </c>
       <c r="J29" s="3" t="s">
-        <v>168</v>
+        <v>111</v>
       </c>
       <c r="K29" s="3">
-        <v>27</v>
+        <v>16</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E30" s="3">
+        <v>8</v>
+      </c>
+      <c r="F30" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="G30" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I30" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="C30" s="3" t="s">
+      <c r="J30" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="D30" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E30" s="3">
-        <v>10</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="G30" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="H30" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I30" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="J30" s="3" t="s">
-        <v>198</v>
-      </c>
       <c r="K30" s="3">
-        <v>17</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>101</v>
+        <v>120</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E31" s="3">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>94</v>
+        <v>165</v>
       </c>
       <c r="K31" s="3">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E32" s="3">
+        <v>4</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="J32" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="B32" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E32" s="3">
-        <v>9</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>116</v>
-      </c>
       <c r="K32" s="3">
-        <v>15</v>
+        <v>71</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E33" s="3">
+        <v>4</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I33" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="B33" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E33" s="3">
-        <v>8</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="G33" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="H33" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I33" s="3" t="s">
-        <v>208</v>
-      </c>
       <c r="J33" s="3" t="s">
-        <v>116</v>
+        <v>71</v>
       </c>
       <c r="K33" s="3">
-        <v>15</v>
+        <v>24</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="C34" s="3" t="s">
         <v>209</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>123</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E34" s="3">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F34" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I34" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="G34" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="H34" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I34" s="3" t="s">
-        <v>212</v>
-      </c>
       <c r="J34" s="3" t="s">
-        <v>213</v>
+        <v>195</v>
       </c>
       <c r="K34" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C35" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="D35" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E35" s="3">
+        <v>0</v>
+      </c>
+      <c r="F35" s="3"/>
+      <c r="G35" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I35" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="C35" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E35" s="3">
-        <v>8</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="G35" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="H35" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I35" s="3" t="s">
-        <v>218</v>
-      </c>
       <c r="J35" s="3" t="s">
-        <v>213</v>
+        <v>77</v>
       </c>
       <c r="K35" s="3">
-        <v>0</v>
+        <v>44</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>199</v>
+        <v>216</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E36" s="3">
-        <v>6</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>221</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>83</v>
+        <v>220</v>
       </c>
       <c r="K36" s="3">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E37" s="3">
-        <v>4</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="G37" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="H37" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I37" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="J37" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="K37" s="3">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E38" s="3">
-        <v>4</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="G38" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="H38" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I38" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="J38" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="K38" s="3">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E39" s="3">
-        <v>4</v>
-      </c>
-      <c r="F39" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="G39" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="H39" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="I39" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="J39" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="K39" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E40" s="3">
-        <v>3</v>
-      </c>
-      <c r="F40" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="G40" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="H40" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I40" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="J40" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="K40" s="3">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E41" s="3">
-        <v>3</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="G41" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="H41" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I41" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="J41" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="K41" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E42" s="3">
-        <v>0</v>
-      </c>
-      <c r="F42" s="3"/>
-      <c r="G42" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="K42" s="3">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E43" s="3">
-        <v>0</v>
-      </c>
-      <c r="F43" s="3"/>
-      <c r="G43" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="J43" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="K43" s="3">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K43"/>
+  <autoFilter ref="A1:K36"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1"/>
     <hyperlink ref="I3" r:id="rId2"/>
@@ -3641,13 +3300,6 @@
     <hyperlink ref="I34" r:id="rId33"/>
     <hyperlink ref="I35" r:id="rId34"/>
     <hyperlink ref="I36" r:id="rId35"/>
-    <hyperlink ref="I37" r:id="rId36"/>
-    <hyperlink ref="I38" r:id="rId37"/>
-    <hyperlink ref="I39" r:id="rId38"/>
-    <hyperlink ref="I40" r:id="rId39"/>
-    <hyperlink ref="I41" r:id="rId40"/>
-    <hyperlink ref="I42" r:id="rId41"/>
-    <hyperlink ref="I43" r:id="rId42"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -3655,11 +3307,11 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="1" max="1" width="47" customWidth="1"/>
+    <col min="2" max="2" width="25" customWidth="1"/>
     <col min="3" max="3" width="24" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="29" customWidth="1"/>
+    <col min="5" max="5" width="59" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
@@ -3678,10 +3330,10 @@
         <v>40</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>44</v>
@@ -3689,33 +3341,33 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>209</v>
+        <v>161</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>210</v>
+        <v>162</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D2" s="3">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>211</v>
+        <v>163</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>212</v>
+        <v>164</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>213</v>
+        <v>165</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>214</v>
+        <v>196</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>215</v>
+        <v>197</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>25</v>
@@ -3724,68 +3376,20 @@
         <v>8</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>217</v>
+        <v>193</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>218</v>
+        <v>198</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D4" s="3">
-        <v>4</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D5" s="3">
-        <v>3</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>213</v>
+        <v>165</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G5"/>
+  <autoFilter ref="A1:G3"/>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1"/>
     <hyperlink ref="F3" r:id="rId2"/>
-    <hyperlink ref="F4" r:id="rId3"/>
-    <hyperlink ref="F5" r:id="rId4"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -3793,185 +3397,185 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="1" max="1" width="17" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
     <col min="3" max="3" width="60" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>254</v>
+        <v>221</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>255</v>
+        <v>222</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>256</v>
+        <v>223</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>229</v>
+        <v>205</v>
       </c>
       <c r="B2" s="3">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>257</v>
+        <v>224</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B3" s="3">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>258</v>
+        <v>226</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>259</v>
+        <v>200</v>
       </c>
       <c r="B4" s="3">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>260</v>
+        <v>227</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>261</v>
+        <v>228</v>
       </c>
       <c r="B5" s="3">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>262</v>
+        <v>229</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>191</v>
+        <v>171</v>
       </c>
       <c r="B6" s="3">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>263</v>
+        <v>230</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>234</v>
+        <v>210</v>
       </c>
       <c r="B7" s="3">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>264</v>
+        <v>231</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>265</v>
+        <v>232</v>
       </c>
       <c r="B8" s="3">
         <v>12</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>266</v>
+        <v>233</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>267</v>
+        <v>234</v>
       </c>
       <c r="B9" s="3">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>268</v>
+        <v>235</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>269</v>
+        <v>236</v>
       </c>
       <c r="B10" s="3">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>270</v>
+        <v>237</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>271</v>
+        <v>238</v>
       </c>
       <c r="B11" s="3">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>272</v>
+        <v>239</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>273</v>
+        <v>240</v>
       </c>
       <c r="B12" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>274</v>
+        <v>241</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>275</v>
+        <v>242</v>
       </c>
       <c r="B13" s="3">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>276</v>
+        <v>243</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>277</v>
+        <v>244</v>
       </c>
       <c r="B14" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>278</v>
+        <v>245</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>279</v>
+        <v>246</v>
       </c>
       <c r="B15" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>280</v>
+        <v>247</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>281</v>
+        <v>248</v>
       </c>
       <c r="B16" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>276</v>
+        <v>249</v>
       </c>
     </row>
   </sheetData>
@@ -3991,10 +3595,10 @@
         <v>39</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>282</v>
+        <v>250</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>283</v>
+        <v>251</v>
       </c>
     </row>
     <row r="2">
@@ -4002,10 +3606,10 @@
         <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>284</v>
+        <v>252</v>
       </c>
     </row>
     <row r="3">
@@ -4013,10 +3617,10 @@
         <v>26</v>
       </c>
       <c r="B3" s="3">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>285</v>
+        <v>253</v>
       </c>
     </row>
     <row r="4">
@@ -4024,10 +3628,10 @@
         <v>27</v>
       </c>
       <c r="B4" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>286</v>
+        <v>254</v>
       </c>
     </row>
     <row r="5">
@@ -4038,7 +3642,7 @@
         <v>2</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>287</v>
+        <v>255</v>
       </c>
     </row>
     <row r="6">
@@ -4049,7 +3653,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>288</v>
+        <v>256</v>
       </c>
     </row>
     <row r="7">
@@ -4060,7 +3664,7 @@
         <v>1</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>289</v>
+        <v>257</v>
       </c>
     </row>
   </sheetData>
@@ -4081,13 +3685,13 @@
         <v>42</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>290</v>
+        <v>258</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>291</v>
+        <v>259</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>292</v>
+        <v>260</v>
       </c>
     </row>
     <row r="2">
@@ -4095,10 +3699,10 @@
         <v>33</v>
       </c>
       <c r="B2" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>293</v>
+        <v>261</v>
       </c>
       <c r="D2" s="3"/>
     </row>
@@ -4107,10 +3711,10 @@
         <v>32</v>
       </c>
       <c r="B3" s="3">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>293</v>
+        <v>261</v>
       </c>
       <c r="D3" s="3"/>
     </row>
@@ -4119,10 +3723,10 @@
         <v>34</v>
       </c>
       <c r="B4" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>293</v>
+        <v>261</v>
       </c>
       <c r="D4" s="3"/>
     </row>

--- a/reports/devops-juniors-israel-2026-W37.xlsx
+++ b/reports/devops-juniors-israel-2026-W37.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="262">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="257">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-11T11:09:59</t>
+    <t xml:space="preserve">2026-09-13T11:41:46</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -100,15 +100,15 @@
     <t xml:space="preserve">Help Desk / IT Support</t>
   </si>
   <si>
+    <t xml:space="preserve">Junior DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
+  </si>
+  <si>
     <t xml:space="preserve">Junior SysAdmin / Linux</t>
   </si>
   <si>
-    <t xml:space="preserve">Junior DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
-  </si>
-  <si>
     <t xml:space="preserve">By source</t>
   </si>
   <si>
@@ -232,462 +232,447 @@
     <t xml:space="preserve">2026-08-18</t>
   </si>
   <si>
-    <t xml:space="preserve">AI Intern</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CertifyOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pune</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, GCP, Cloud (any), Kubernetes, CI/CD, Git, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-ai-intern-certifyos-1135555</t>
+    <t xml:space="preserve">Software Engineer Student, SPIV team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amazon Web Services (AWS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, CI/CD, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-student-spiv-team-at-amazon-web-services-aws-4456348779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Production Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Torq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6179167004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer (NOC / Tier 1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kela Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-noc-tier-1-at-kela-technologies-4461059776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upwind Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Networking, Monitoring, Databases, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-upwind-security-4460871956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lumana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-lumana-4463708633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Cloud Security Engineer (Entry-Level)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OnCloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cloud-security-engineer-entry-level-at-oncloud-4456904380</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TytoCare</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-tytocare-4461579939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator - 243425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experis Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-243425-at-experis-israel-4461821675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Engineering INTERN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Cloud (any), CI/CD, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineering-intern-at-microsoft-4451071541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gini-Apps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Networking, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-gini-apps-4440026223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Communication System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ceva, Inc.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/communication-system-engineer-at-ceva-inc-4459357209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hillcrest Labs, acquired by CEVA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/communication-system-engineer-at-hillcrest-labs-acquired-by-ceva-4457713529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fetcherr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, CI/CD, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-fetcherr-4449296509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Field Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mornex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-field-support-engineer-at-mornex-4457946363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator (24/7 Shift-Based)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">evoke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-24-7-shift-based-at-evoke-4462157700</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Systems Engineer 2, Technical Operations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oracle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineer-2-technical-operations-at-oracle-4444274357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring Technical Support Specialist (NOC)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SuperCom (NASDAQ: SPCB)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Cloud (any), Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/monitoring-technical-support-specialist-noc-at-supercom-nasdaq-spcb-4465838312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tata Consultancy Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-tata-consultancy-services-4459788315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WaveBL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc%0A%09%09%09%09%09%09%09%09%09%0A%09%09%09%09%09%09%09%09%0A%09%09%09%09%09%09%09%09%09%09israel-at-wavebl-4443917908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs JD Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estonia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COM-C-TECH LTD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory, Windows Server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-administrator-at-com-c-tech-ltd-4457234117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Platform Engineer - Student (Java)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-engineer-student-java-at-sap-4457493270</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PassportCard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-at-passportcard-4458103759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Engineer- Student Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Global-e</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-student-position-at-global-e-4463461048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Employer Branding Student (Temporary )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4912601101?gh_jid=4912601101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operations Engineer II</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWeber</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uluberia-II,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-operations-engineer-ii-aweber-1136778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Working Student, Legal (German-speaking)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Via</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Berlin, Germany</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/via/jobs/8585955002</t>
   </si>
   <si>
     <t xml:space="preserve">2026-07-29</t>
   </si>
   <si>
-    <t xml:space="preserve">Software Engineer Student, SPIV team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Amazon Web Services (AWS)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, CI/CD, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-student-spiv-team-at-amazon-web-services-aws-4456348779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Production Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Torq</t>
-  </si>
-  <si>
-    <t xml:space="preserve">israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6179167004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer (NOC / Tier 1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kela Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-noc-tier-1-at-kela-technologies-4461059776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upwind Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Networking, Monitoring, Databases, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-upwind-security-4460871956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lumana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-lumana-4463708633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Cloud Security Engineer (Entry-Level)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OnCloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cloud-security-engineer-entry-level-at-oncloud-4456904380</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TytoCare</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-tytocare-4461579939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator - 243425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experis Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-243425-at-experis-israel-4461821675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Engineering INTERN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Cloud (any), CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineering-intern-at-microsoft-4451071541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raft Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4433796227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gini-Apps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Networking, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-gini-apps-4440026223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Communication System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ceva, Inc.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/communication-system-engineer-at-ceva-inc-4459357209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fetcherr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-fetcherr-4449296509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Field Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mornex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-field-support-engineer-at-mornex-4457946363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator (24/7 Shift-Based)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">evoke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-24-7-shift-based-at-evoke-4462157700</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring Technical Support Specialist (NOC)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SuperCom (NASDAQ: SPCB)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Cloud (any), Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/monitoring-technical-support-specialist-noc-at-supercom-nasdaq-spcb-4465838312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tata Consultancy Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-tata-consultancy-services-4459788315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WaveBL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc%0A%09%09%09%09%09%09%09%09%09%0A%09%09%09%09%09%09%09%09%0A%09%09%09%09%09%09%09%09%09%09israel-at-wavebl-4443917908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs JD Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days Open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optimove</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estonia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COM-C-TECH LTD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory, Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-administrator-at-com-c-tech-ltd-4457234117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Platform Engineer - Student (Java)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-engineer-student-java-at-sap-4457493270</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PassportCard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-at-passportcard-4458103759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Engineer- Student Position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Global-e</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-student-position-at-global-e-4463461048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Employer Branding Student (Temporary )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4912601101?gh_jid=4912601101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Power Control System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SolarEdge Technologies</t>
+    <t xml:space="preserve">Student Success Coach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FindTutors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">London, London, England, United Kingdom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-student-success-coach-findtutors-1136086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roles requiring it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What to learn / where to start</t>
   </si>
   <si>
     <t xml:space="preserve">Troubleshooting</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-power-control-system-engineer-at-solaredge-technologies-4438264844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Operations Engineer II</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWeber</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Uluberia-II,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-operations-engineer-ii-aweber-1136778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Working Student, Legal (German-speaking)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Via</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Berlin, Germany</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/via/jobs/8585955002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Student Success Coach</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FindTutors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">London, London, England, United Kingdom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-student-success-coach-findtutors-1136086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roles requiring it</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What to learn / where to start</t>
-  </si>
-  <si>
     <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
   </si>
   <si>
@@ -700,15 +685,15 @@
     <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
   </si>
   <si>
+    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
+  </si>
+  <si>
     <t xml:space="preserve">Python</t>
   </si>
   <si>
     <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
   </si>
   <si>
-    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
-  </si>
-  <si>
     <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
   </si>
   <si>
@@ -718,28 +703,34 @@
     <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
   </si>
   <si>
+    <t xml:space="preserve">Bash/Shell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
+  </si>
+  <si>
     <t xml:space="preserve">CI/CD</t>
   </si>
   <si>
     <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
   </si>
   <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free Docker Get Started tutorial + build 3 home-lab containers</t>
   </si>
   <si>
     <t xml:space="preserve">Kubernetes</t>
@@ -748,12 +739,6 @@
     <t xml:space="preserve">kubernetes.io tutorials → minikube on laptop → KCNA cert</t>
   </si>
   <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free Docker Get Started tutorial + build 3 home-lab containers</t>
-  </si>
-  <si>
     <t xml:space="preserve">GCP</t>
   </si>
   <si>
@@ -781,13 +766,13 @@
     <t xml:space="preserve">Tier 1/2 → SysAdmin → Junior DevOps. ~24 month path.</t>
   </si>
   <si>
+    <t xml:space="preserve">Direct DevOps role — apply aggressively. Rare and competitive.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Often paired with on-call. Strong learning track.</t>
+  </si>
+  <si>
     <t xml:space="preserve">12-18 months → Junior DevOps. Strengthen Linux + Python + AWS.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Direct DevOps role — apply aggressively. Rare and competitive.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Often paired with on-call. Strong learning track.</t>
   </si>
   <si>
     <t xml:space="preserve">Jobs</t>
@@ -924,7 +909,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7">
@@ -932,7 +917,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -940,7 +925,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
@@ -948,7 +933,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>513</v>
+        <v>498</v>
       </c>
     </row>
     <row r="10">
@@ -1030,7 +1015,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="22">
@@ -1038,7 +1023,7 @@
         <v>26</v>
       </c>
       <c r="B22" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23">
@@ -1054,7 +1039,7 @@
         <v>28</v>
       </c>
       <c r="B24" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1104,7 +1089,7 @@
         <v>34</v>
       </c>
       <c r="B31" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -1116,7 +1101,7 @@
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
-    <col min="3" max="3" width="32" customWidth="1"/>
+    <col min="3" max="3" width="34" customWidth="1"/>
     <col min="4" max="4" width="42" customWidth="1"/>
     <col min="5" max="5" width="31" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
@@ -1204,7 +1189,7 @@
         <v>53</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
@@ -1335,19 +1320,19 @@
         <v>26</v>
       </c>
       <c r="F7" s="3">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>75</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I7" s="3" t="s">
         <v>76</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>77</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8">
@@ -1355,31 +1340,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="D8" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="E8" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F8" s="3">
+        <v>68</v>
+      </c>
+      <c r="G8" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F8" s="3">
-        <v>70</v>
-      </c>
-      <c r="G8" s="3" t="s">
+      <c r="H8" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I8" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="H8" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I8" s="3" t="s">
+      <c r="J8" s="3" t="s">
         <v>82</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="9">
@@ -1393,25 +1378,25 @@
         <v>84</v>
       </c>
       <c r="D9" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F9" s="3">
+        <v>61</v>
+      </c>
+      <c r="G9" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="E9" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F9" s="3">
-        <v>68</v>
-      </c>
-      <c r="G9" s="3" t="s">
+      <c r="H9" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I9" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="H9" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I9" s="3" t="s">
+      <c r="J9" s="3" t="s">
         <v>87</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="10">
@@ -1419,19 +1404,19 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="D10" s="3" t="s">
         <v>90</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>53</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>27</v>
       </c>
       <c r="F10" s="3">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>91</v>
@@ -1492,10 +1477,10 @@
         <v>102</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F12" s="3">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>103</v>
@@ -1524,10 +1509,10 @@
         <v>108</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F13" s="3">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>109</v>
@@ -1571,7 +1556,7 @@
         <v>116</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>117</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -1579,31 +1564,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="D15" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="E15" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F15" s="3">
+        <v>39</v>
+      </c>
+      <c r="G15" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="E15" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F15" s="3">
-        <v>44</v>
-      </c>
-      <c r="G15" s="3" t="s">
+      <c r="H15" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I15" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="H15" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>122</v>
-      </c>
       <c r="J15" s="3" t="s">
-        <v>105</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16">
@@ -1611,28 +1596,28 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="D16" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F16" s="3">
+        <v>28</v>
+      </c>
+      <c r="G16" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="H16" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I16" s="3" t="s">
         <v>125</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F16" s="3">
-        <v>39</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>127</v>
       </c>
       <c r="J16" s="3" t="s">
         <v>50</v>
@@ -1643,31 +1628,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F17" s="3">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>132</v>
+        <v>87</v>
       </c>
     </row>
     <row r="18">
@@ -1675,13 +1660,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>25</v>
@@ -1690,16 +1675,16 @@
         <v>28</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>50</v>
+        <v>132</v>
       </c>
     </row>
     <row r="19">
@@ -1707,31 +1692,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F19" s="3">
+        <v>27</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I19" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="J19" s="3" t="s">
         <v>137</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F19" s="3">
-        <v>28</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="20">
@@ -1739,13 +1724,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="D20" s="3" t="s">
         <v>140</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>114</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>27</v>
@@ -1754,16 +1739,16 @@
         <v>27</v>
       </c>
       <c r="G20" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I20" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I20" s="3" t="s">
+      <c r="J20" s="3" t="s">
         <v>143</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="21">
@@ -1771,31 +1756,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="D21" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="D21" s="3" t="s">
+      <c r="E21" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F21" s="3">
+        <v>24</v>
+      </c>
+      <c r="G21" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="E21" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F21" s="3">
-        <v>27</v>
-      </c>
-      <c r="G21" s="3" t="s">
+      <c r="H21" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I21" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="H21" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I21" s="3" t="s">
+      <c r="J21" s="3" t="s">
         <v>149</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="22">
@@ -1803,13 +1788,13 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="C22" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="C22" s="3" t="s">
-        <v>152</v>
-      </c>
       <c r="D22" s="3" t="s">
-        <v>153</v>
+        <v>114</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>25</v>
@@ -1818,16 +1803,16 @@
         <v>24</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>156</v>
+        <v>137</v>
       </c>
     </row>
     <row r="23">
@@ -1835,13 +1820,13 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>25</v>
@@ -1850,16 +1835,16 @@
         <v>24</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="24">
@@ -1867,10 +1852,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>53</v>
@@ -1882,16 +1867,16 @@
         <v>23</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="25">
@@ -1899,13 +1884,13 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>25</v>
@@ -1914,16 +1899,16 @@
         <v>12</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
     </row>
     <row r="26">
@@ -1931,13 +1916,13 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>25</v>
@@ -1946,16 +1931,16 @@
         <v>12</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
     </row>
   </sheetData>
@@ -1994,7 +1979,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="32" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="31" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
@@ -2008,7 +1993,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>37</v>
@@ -2023,22 +2008,22 @@
         <v>40</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>42</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>44</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
     </row>
     <row r="2">
@@ -2061,7 +2046,7 @@
         <v>48</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>32</v>
@@ -2073,7 +2058,7 @@
         <v>50</v>
       </c>
       <c r="K2" s="3">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3">
@@ -2087,7 +2072,7 @@
         <v>53</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E3" s="3">
         <v>100</v>
@@ -2096,7 +2081,7 @@
         <v>54</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>32</v>
@@ -2108,7 +2093,7 @@
         <v>56</v>
       </c>
       <c r="K3" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -2131,7 +2116,7 @@
         <v>59</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>32</v>
@@ -2143,7 +2128,7 @@
         <v>50</v>
       </c>
       <c r="K4" s="3">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5">
@@ -2166,7 +2151,7 @@
         <v>64</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>33</v>
@@ -2178,7 +2163,7 @@
         <v>66</v>
       </c>
       <c r="K5" s="3">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6">
@@ -2201,7 +2186,7 @@
         <v>69</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>32</v>
@@ -2213,7 +2198,7 @@
         <v>71</v>
       </c>
       <c r="K6" s="3">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7">
@@ -2230,60 +2215,60 @@
         <v>26</v>
       </c>
       <c r="E7" s="3">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>75</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I7" s="3" t="s">
         <v>76</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>77</v>
+        <v>50</v>
       </c>
       <c r="K7" s="3">
-        <v>44</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="C8" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="D8" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8" s="3">
+        <v>68</v>
+      </c>
+      <c r="F8" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E8" s="3">
-        <v>70</v>
-      </c>
-      <c r="F8" s="3" t="s">
+      <c r="G8" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I8" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I8" s="3" t="s">
+      <c r="J8" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="J8" s="3" t="s">
-        <v>50</v>
-      </c>
       <c r="K8" s="3">
-        <v>22</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9">
@@ -2294,54 +2279,54 @@
         <v>84</v>
       </c>
       <c r="C9" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E9" s="3">
+        <v>61</v>
+      </c>
+      <c r="F9" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E9" s="3">
-        <v>68</v>
-      </c>
-      <c r="F9" s="3" t="s">
+      <c r="G9" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I9" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I9" s="3" t="s">
+      <c r="J9" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="J9" s="3" t="s">
-        <v>88</v>
-      </c>
       <c r="K9" s="3">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="C10" s="3" t="s">
         <v>90</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>53</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>27</v>
       </c>
       <c r="E10" s="3">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>91</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>32</v>
@@ -2353,7 +2338,7 @@
         <v>93</v>
       </c>
       <c r="K10" s="3">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11">
@@ -2376,7 +2361,7 @@
         <v>97</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>32</v>
@@ -2388,7 +2373,7 @@
         <v>99</v>
       </c>
       <c r="K11" s="3">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
@@ -2402,16 +2387,16 @@
         <v>102</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E12" s="3">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>103</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>32</v>
@@ -2423,7 +2408,7 @@
         <v>105</v>
       </c>
       <c r="K12" s="3">
-        <v>5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13">
@@ -2437,16 +2422,16 @@
         <v>108</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E13" s="3">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>109</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>32</v>
@@ -2458,7 +2443,7 @@
         <v>111</v>
       </c>
       <c r="K13" s="3">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14">
@@ -2481,7 +2466,7 @@
         <v>115</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>32</v>
@@ -2490,126 +2475,126 @@
         <v>116</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>117</v>
+        <v>99</v>
       </c>
       <c r="K14" s="3">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="C15" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="D15" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E15" s="3">
+        <v>39</v>
+      </c>
+      <c r="F15" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E15" s="3">
-        <v>44</v>
-      </c>
-      <c r="F15" s="3" t="s">
+      <c r="G15" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I15" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="G15" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>122</v>
-      </c>
       <c r="J15" s="3" t="s">
-        <v>105</v>
+        <v>50</v>
       </c>
       <c r="K15" s="3">
-        <v>5</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="B16" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="C16" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E16" s="3">
+        <v>28</v>
+      </c>
+      <c r="F16" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="G16" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I16" s="3" t="s">
         <v>125</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E16" s="3">
-        <v>39</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>127</v>
       </c>
       <c r="J16" s="3" t="s">
         <v>50</v>
       </c>
       <c r="K16" s="3">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E17" s="3">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>132</v>
+        <v>87</v>
       </c>
       <c r="K17" s="3">
-        <v>60</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>25</v>
@@ -2618,68 +2603,68 @@
         <v>28</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>50</v>
+        <v>132</v>
       </c>
       <c r="K18" s="3">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E19" s="3">
+        <v>27</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I19" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="J19" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="C19" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E19" s="3">
-        <v>28</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>93</v>
-      </c>
       <c r="K19" s="3">
-        <v>11</v>
+        <v>30</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>140</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>114</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>27</v>
@@ -2688,68 +2673,68 @@
         <v>27</v>
       </c>
       <c r="F20" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I20" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I20" s="3" t="s">
+      <c r="J20" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="J20" s="3" t="s">
-        <v>144</v>
-      </c>
       <c r="K20" s="3">
-        <v>28</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B21" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="C21" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="D21" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E21" s="3">
+        <v>24</v>
+      </c>
+      <c r="F21" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E21" s="3">
-        <v>27</v>
-      </c>
-      <c r="F21" s="3" t="s">
+      <c r="G21" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I21" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="G21" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I21" s="3" t="s">
+      <c r="J21" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="J21" s="3" t="s">
-        <v>150</v>
-      </c>
       <c r="K21" s="3">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="B22" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>152</v>
-      </c>
       <c r="C22" s="3" t="s">
-        <v>153</v>
+        <v>114</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>25</v>
@@ -2758,33 +2743,33 @@
         <v>24</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>156</v>
+        <v>137</v>
       </c>
       <c r="K22" s="3">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>25</v>
@@ -2793,30 +2778,30 @@
         <v>24</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="K23" s="3">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>53</v>
@@ -2828,33 +2813,33 @@
         <v>23</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="K24" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>25</v>
@@ -2863,33 +2848,33 @@
         <v>12</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="K25" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>25</v>
@@ -2898,33 +2883,33 @@
         <v>12</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="K26" s="3">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>27</v>
@@ -2933,62 +2918,62 @@
         <v>10</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>33</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="K27" s="3">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E28" s="3">
         <v>9</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="H28" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="K28" s="3">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>46</v>
@@ -3003,33 +2988,33 @@
         <v>8</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="K29" s="3">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>25</v>
@@ -3038,33 +3023,33 @@
         <v>8</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="K30" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>25</v>
@@ -3073,27 +3058,27 @@
         <v>8</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="K31" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>62</v>
@@ -3108,103 +3093,101 @@
         <v>4</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>33</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="K32" s="3">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>153</v>
+        <v>202</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E33" s="3">
         <v>4</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>71</v>
+        <v>192</v>
       </c>
       <c r="K33" s="3">
-        <v>24</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="C34" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="D34" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E34" s="3">
+        <v>0</v>
+      </c>
+      <c r="F34" s="3"/>
+      <c r="G34" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I34" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="C34" s="3" t="s">
+      <c r="J34" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="D34" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E34" s="3">
-        <v>4</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="G34" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H34" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="I34" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="J34" s="3" t="s">
-        <v>195</v>
-      </c>
       <c r="K34" s="3">
-        <v>1</v>
+        <v>46</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="C35" s="3" t="s">
         <v>212</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>214</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>26</v>
@@ -3214,56 +3197,23 @@
       </c>
       <c r="F35" s="3"/>
       <c r="G35" s="3" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>77</v>
+        <v>214</v>
       </c>
       <c r="K35" s="3">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E36" s="3">
-        <v>0</v>
-      </c>
-      <c r="F36" s="3"/>
-      <c r="G36" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H36" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="I36" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="J36" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="K36" s="3">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K36"/>
+  <autoFilter ref="A1:K35"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1"/>
     <hyperlink ref="I3" r:id="rId2"/>
@@ -3299,7 +3249,6 @@
     <hyperlink ref="I33" r:id="rId32"/>
     <hyperlink ref="I34" r:id="rId33"/>
     <hyperlink ref="I35" r:id="rId34"/>
-    <hyperlink ref="I36" r:id="rId35"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -3307,11 +3256,11 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="47" customWidth="1"/>
-    <col min="2" max="2" width="25" customWidth="1"/>
-    <col min="3" max="3" width="24" customWidth="1"/>
+    <col min="1" max="1" width="31" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="59" customWidth="1"/>
+    <col min="5" max="5" width="37" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
@@ -3330,10 +3279,10 @@
         <v>40</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>44</v>
@@ -3341,55 +3290,31 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>161</v>
+        <v>126</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>162</v>
+        <v>130</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D2" s="3">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>163</v>
+        <v>128</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>164</v>
+        <v>131</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D3" s="3">
-        <v>8</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>165</v>
+        <v>132</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G3"/>
+  <autoFilter ref="A1:G2"/>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1"/>
-    <hyperlink ref="F3" r:id="rId2"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -3404,178 +3329,178 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>205</v>
+        <v>218</v>
       </c>
       <c r="B2" s="3">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="B3" s="3">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="B4" s="3">
         <v>16</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>228</v>
+        <v>168</v>
       </c>
       <c r="B5" s="3">
         <v>13</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>171</v>
+        <v>224</v>
       </c>
       <c r="B6" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="B7" s="3">
         <v>12</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="B8" s="3">
         <v>12</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="B9" s="3">
         <v>9</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="B10" s="3">
         <v>8</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="B11" s="3">
         <v>8</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="B12" s="3">
         <v>8</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="B13" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="B14" s="3">
         <v>6</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="B15" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="B16" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
     </row>
   </sheetData>
@@ -3595,10 +3520,10 @@
         <v>39</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
     </row>
     <row r="2">
@@ -3606,10 +3531,10 @@
         <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
     </row>
     <row r="3">
@@ -3617,10 +3542,10 @@
         <v>26</v>
       </c>
       <c r="B3" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
     </row>
     <row r="4">
@@ -3631,7 +3556,7 @@
         <v>7</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
     </row>
     <row r="5">
@@ -3639,10 +3564,10 @@
         <v>28</v>
       </c>
       <c r="B5" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
     </row>
     <row r="6">
@@ -3653,7 +3578,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
     </row>
     <row r="7">
@@ -3664,7 +3589,7 @@
         <v>1</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
     </row>
   </sheetData>
@@ -3685,13 +3610,13 @@
         <v>42</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
     </row>
     <row r="2">
@@ -3702,7 +3627,7 @@
         <v>5</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="D2" s="3"/>
     </row>
@@ -3714,7 +3639,7 @@
         <v>28</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="D3" s="3"/>
     </row>
@@ -3723,10 +3648,10 @@
         <v>34</v>
       </c>
       <c r="B4" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="D4" s="3"/>
     </row>
